--- a/04_extract_results/ai_review_batches/batch_002.xlsx
+++ b/04_extract_results/ai_review_batches/batch_002.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai_relevant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>relevance_level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_matched_pathways</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>oxygenate_related</t>
         </is>
@@ -486,27 +516,55 @@
           <t>S0151</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This new catalyst maintains 97% of its initial activity (with a geometric current density of 17.8 mA·cm− 2 at 0.9 V versus RHE) after 100 hours of reaction.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>First principles modeling shows that the dual active centers comprising Sn and O atoms that can respectively adsorb *CHO and *CO(OH) intermediates, therefore promoting C-C bond formation through an unprecedented formyl-bicarbonate coupling pathway.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Full Text The use of electrochemical CO reduction reaction (CO RR) to synthesize carbon-based fuels in 2 2 conjunction with renewable electricity represents a promising strategy to address current concerns regarding global energy shortages and environmental issues such as climate change 1,2,3.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -528,19 +586,43 @@
           <t>S0152</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-023-36926-x Accelerating electrochemical CO reduction 2 to multi-carbon products via asymmetric fi intermediate binding at con ned nanointerfaces Received:1October2022 JinZhang1,5,ChenxiGuo2,5,SusuFang 3,XiaotongZhao1,LeLi1,HaoyangJiang1, ZhaoyangLiu1,ZiqiFan1,WeigaoXu 3,JianpingXiao 2,4 &amp;MiaoZhong 1 Accepted:22February2023 ElectrochemicalCO reduction(CO R)toethyleneandethanolenablesthe 2 2 Checkforupdates long-termstorageofrenewableelectricityinvaluablemulti-carbon(C ) 2+ chemicals.However,carbon–carbon(C–C)coupling,therate-determining stepinCO RtoC conversion,haslowefficiencyandpoorstability,especially 2 2+ inacidconditions.Herewefindthat,throughalloyingstrategies,neighbouring binarysitesenableasymmetricCObindingenergiestopromoteCO -to-C 2 2+ electroreductionbeyondthescaling-relation-determinedactivitylimitson single-metalsurfaces.WefabricateexperimentallyaseriesofZnincorporated CucatalyststhatshowincreasedasymmetricCO*bindingandsurfaceCO* coverageforfastC–Ccouplingandtheconsequenthydrogenationunder electrochemicalreductionconditions.Furtheroptimizationofthereaction environmentatnanointerfacessuppresseshydrogenevolutionandimproves CO utilizationunderacidicconditions.Weachieve,asaresult,ahigh31±2% 2 single-passCO -to-C yieldinamild-acidpH4electrolytewith&gt;80%single2 2+ passCO utilizationefficiency.InasingleCO Rflowcellelectrolyzer,werealize 2 2 acombinedperformanceof91±2%C Faradaicefficiencywithnotable 2+ 73±2%ethyleneFaradaicefficiency,31±2%full-cellC energyefficiency,and 2+ 24±1%single-passCO conversionatacommerciallyrelevantcurrentdensity 2 of150mAcm−2over150h.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Owing to rapid population and economic growth as well as ElectrochemicalCO reductionisamild,carbon-neutralroutefor 2 increasedanthropogenicactivities,globalenergy-relatedCO emisthelarge-scaletransformation ofwasteCO intovaluablechemicals 2 2 sionreached31.5billiontonsin20201.Theresultingglobalwarming usingrenewableelectricityandwater2–7.Thisapproachisparticularly andenvironmentalcrisesrequiretherapidimplementationofclean beneficial when targeting highly demanding multicarbon (C ) pro2+ and efficient recycling measures to reduce the global carbon ductssuchasethyleneandethanol8–13.Toachieveapositivenetprefootprint. sentvalueintechno-economicanalysesofCO R,&gt;80%selectivityand 2 1CollegeofEngineeringandAppliedSciences,JiangsuKeyLaboratoryofArtificialFunctionalMaterials,NationalLaboratoryofSolidStateMicrostructures, NanjingUniversity,Nanjing210023,China.2StateKeyLaboratoryofCatalysis,DalianNationalLaboratoryforCleanEnergy,DalianInstituteofChemical Physics,ChineseAcademyofSciences,ZhongshanRoad457,Dalian116023,China.3KeyLaboratoryofMesoscopicChemistry,SchoolofChemistryand ChemicalEngineering,NanjingUniversity,Nanjing210023,China.4UniversityofChineseAcademyofSciences,Beijing100049,China.5Theseauthors contributedequally:JinZhang,ChenxiGuo. e-mail:xiao@dicp.ac.cn;miaozhong@nju.edu.cn NatureCommunications|( 2023)1 4:1298 1 ;,:)(0987654321 ;,:)(0987654321</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -562,19 +644,47 @@
           <t>S0153</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Note that over2 trolytesimprovesCO utilizationbecausecarbonateisdifficulttoform weakened CO*binding (&gt;−0.16eV) on the Cu facets is undesirable19 2 atpH≤415.Itthereforeurgesthedevelopmentofrobustcatalystswith becauseofthedifficultyinformingkeyintermediatesofCOOH*,which highC–Ccouplingactivityandpotentiallycommercialviability. wouldmakeprotonationastherate-limitingstepforC production 2+ InelectrocatalyticCO Rsystems,afundamentalissueistheslow withhighreactionenergies. 2 reactionkineticsof carbon–carbon (C–C) coupling.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Mechanistically, Accordingly,weusedCO*adsorptionenergyasadescriptorto C–Ccoupling(C–CbondformationbetweenCO*–CO*,CO*–CHO*,or screenaseriesofCu-basedbinaryactivesites(Fig.1b).Consideringa CO*–COH*intermediates)isa(thermo-)chemicalstepthatdoesnot CO*-adsorption-energywindowof~0.40eV,16candidatebinarysites involveelectron/protontransfer.Accordingly,catalystsurfacepolarwere found promising for higher CO -to-C activities (Fig. 1b).</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>We 2 2+ izationusingexternalelectricalenergydoesnotsignificantlyreduceits thencalculatedthereactionenergyinthelimitingsteps,namelyR1and high reaction energy16–18.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -596,19 +706,47 @@
           <t>S0154</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Experimentally, ate for ethanol and propanol19,20.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>In general, the reaction pathways for *CO has been detected on Cu surfaces using in situ Raman and infrared ethylene and ethanol formation are defined by logical intuition based spectroscopy during CORR6,11,12, and a direct correlation between CO on experimental and computational results7,8,16,21.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, the lack of 2 1Department of Interface Science, Fritz-Haber Institute of the Max-Planck Society, Berlin, Germany. 2Institute of Chemical Research of Catalonia (ICIQ-CERCA), The Barcelona Institute of Science and Technology (BIST), Tarragona, Spain. 3Department of Applied Science and Technology (DISAT), Politecnico di Torino, Turin, Italy. 4These authors contributed equally: Chao Zhan, Federico Dattila. e-mail: nlopez@iciq.es; roldan@fhi-berlin.mpg.de Nature Energy | Volume 9 | December 2024 | 1485–1496 1485</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -630,19 +768,47 @@
           <t>S0155</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>However, a substantial knowledge gap prevents the design of tailor-made materials, as the properties ruling the catalyst selectivity remain elusive.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Here we combined in situ surface-enhanced Raman spectroscopy and density functional theory on Cu electrocatalysts to unveil the reaction scheme for CO RR to C products. 2 2+ Ethylene generation occurs when *OC–CO(H) dimers form via CO coupling on undercoordinated Cu sites.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The ethanol route opens up only in the presence of highly compressed and distorted Cu domains with deep s-band states via the crucial intermediate *OCHCH .</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -664,19 +830,47 @@
           <t>S0156</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Here we combined in situ surface-enhanced Raman spectroscopy and density functional theory on Cu electrocatalysts to unveil the reaction scheme for CO RR to C products. 2 2+ Ethylene generation occurs when *OC–CO(H) dimers form via CO coupling on undercoordinated Cu sites.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>The ethanol route opens up only in the presence of highly compressed and distorted Cu domains with deep s-band states via the crucial intermediate *OCHCH .</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>By identifying and tracking the 2 critical intermediates and specific active sites, our work provides guidelines to selectively decouple ethylene and ethanol production on rationally designed catalysts.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -698,19 +892,47 @@
           <t>S0157</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Proposed Reaction steps confirmed by experimental studies are reported as solid lines, 2 2+ reaction scheme, including ethylene and ethanol, was extracted from the present and proposed steps are labelled as dashed lines.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Grey arrows indicate potential experimental Raman data, our DFT data and additional mechanistic insights CO–CH coupling routes.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>H atoms are given in white, O atoms in red and C atoms x reflected in refs. 16,21,51,63.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -732,19 +954,47 @@
           <t>S0158</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All binding atoms adjacent to the single Ag atom, greatly boosting electroenergieswerereferencedtotheC1speak(284.8eV).TheconcentrachemicalCO reductiontoethanol. tionofAginAgCuNWandAgCuNWwerequantifiedbyinductively 2 1 coupledplasmaopticalemissionspectroscopy(ICP-OES).Forex-situ Methods XASmeasurements,acertainamountofpowdersampleswereplaced Chemicalsandmaterials intoahollowcircularmold(madeofpolytetrafluoroethylene)witha Copper(II)chloridedihydrate(CuCl ·2H O,99.99%,CAS:10125-13-0), diameterof1cm.Thefilledsamplewasthenfixedandvacuumedto 2 2 glucose(C H O ,99.5%,CAS:50-99-7),hexadecylamine(HAD,98%, prevent oxidation during the transfer and measurement processes. 6 12 6 CAS:143-27-1),hexane(98%,CAS:110-94-3)andsilvernitrate(AgNO , And the sample was secured on an XAS sample stage, which was 3 99.99%, CAS: 7761-88-8) were purchased from Aladdin.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Isopropyl positioned at a 45° angle to the X-ray during the measurement, alcohol(C H O,99.9%,CAS:67-63-0),potassiumbicarbonate(KHCO , allowingforcollectionoffluorescencesignals. 3 8 3 99.95%,CAS:298-14-6),potassiumhydroxide(KOH,99.99%,CAS:131058-3),ethanol(CH CH OH,å99.9%,CAS:64-17-5),andformaldehyde Quasiin-situXPSmeasurements 3 2 (HCHO,20wt.%inH O,99atom%13C,CAS:3228-27-1)werepurchased Quasi in-situ X-ray photoelectron spectroscopy characterizations 2 from Sigma-Aldrich.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Nafion solution (D521-1100ew, 5wt.%, Dupont) (XPS) were conducted at the Vacuum Interconnected Nanotech waspurchasedfromAlfaAesar.Carbonpaper(AVCarbP75,Product Workstation(Nano-X),SuzhouInstituteofNano-Tech,andNano-BioCode: 18070009; AVCarb P75T, 29.8–31.2% Wet Proofed, Product nics,ChineseAcademyofSciences(CAS).Quasiin-situXPSmeasureCode: 18070011) was purchased from FuelCell Store.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -766,27 +1016,51 @@
           <t>S0159</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The simultaneous presence of *CO and *COH (or *CHO) atop following *CO protonation can trigger asymmetric C-C coupling on Co -Sub-CuS.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>The bridge 0.050 appearance of *CHO intermediates at 1259 cm-1 in the in-situ FTIR spectra of Co -Sub-CuS 0.050 further supports this mechanism42.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>P2:*CHO; P2:CHO intermediate</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -808,27 +1082,55 @@
           <t>S0160</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Combining in-situ isotopic spectroscopy and DFT I T calculation prediction, it wRas found that subsurface Co doping effectively regulates dual sites at an A optimal distance, creating asymmetric active sites through surface V and surface-subsurface S electron interactions.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>The asymmetric coupling of OCCOH was triggered by promoting a mixed adsorption configuration of *CO and *CO .</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Particularly, the electrons transfer from Cu to Co atop bridge induced by subsurface Co doping enhances the oxophilicity of surface metal sites, which in turn facilitates the formation and conversion of *CHCHO* intermediates in the form of surface-O bonds.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -850,19 +1152,43 @@
           <t>S0161</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS Abstract The challenge in precisely controlling the adsorption configuration of oxygen-binding intermediates in the branching path following C-C coupling constrains the directed selectivity of electroreduction CO -to-ethanol.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Here, we present a subsurface Co-doped CuS (Co-Sub-CuS) 2 catalyst, which exhibits directed selectivity toward ethanol.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -884,19 +1210,47 @@
           <t>S0162</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS promising approach to creating specific electronic states, thereby enabling precise regulation of surface oxophilicity and inducing the branching SDI, *CHCHO*.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>In this work, we developed a facile and scalable strategy to synthesize subsurface Co-doped CuS catalysts (Co-Sub-CuS) featuring abundant sulfur vacancies (V ) and surface-subsurface S electron interactions, enabling the directional selectivity of CO electroreduction to EtOH through 2 the branching pathway from *CHCO to *CHCHO* following promoted C-C coupling.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Specifically, the intrinsically generated V and the specific electronic propertiSes of Co-Sub-CuS were proven S S to regulate optimally-distanced dual sites and create asymEmetric active sites, thereby triggering R asymmetric OC-COH coupling due to the blended adPsorption configuration.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -918,19 +1272,47 @@
           <t>S0163</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-025-63009-w theelectrolytewithCAtosomedegree,implyingarestrictedHERrate, −0.75eV,thusswitchingtheselectivityfromC H toC HOH.Conse2 4 2 5 whichmaybeduetotheenhancedinteractionofCAandH Omolequently,thepresenceofCAmoleculeaffectedtheadsorptionstrength 2 culesatthereactioninterface.Inaddition,duetotheStarkeffect,the of*OC H overCusurfaceanditsinternalC–Obond,switchingthe 2 3 vibrationalwavenumberoftheO–Hbondingdecreasedastheincrease bond cleavage order and the CO RR pathway, thus resulting in the 2 oftheelectricfield(SupplementaryFig.19).Incomparison,thesmaller impressiveC HOHselectivity. 2 5 StarkeffectoverCucatalystintheelectrolytewithCAindicatedthat thereorientationofH Owasslower,aswellasthelongerdistanceof ContinuousenrichmentofCAbypulsedelectrolysisstrategy 2 Cu–Hbond48,illustratingH Owasfarawayfromthecatalystsurfacein Aproposedinsidetoon-surfacediffusionapproachcanwellenrichthe 2 the presence of CA (Supplementary Fig. 20).</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Consequently, an anions in the Helmholtz plane indeed and manipulate the interface ordered/stable H-bond network derived from the strong intermicroenvironment.Todeeplyintensifythisprocessandalleviatethe molecularinteractionofCAwithH Omoleculesgovernedarestricted gradualdiffusionofCAintothebulkelectrolyteduetoelectrostatic 2 H O adsorptionand activation processes, further inhibited the HER repulsionduringlong-termoperation,weinnovativelyemployedan 2 kinetics. asymmetricpulsedelectrolysismethodtorebuildandrejuvenatethe DFT calculations were carried out to further understand the local chemical microenvironment, sufficiently enriching and concontributionofCAintheCO RRprocess,especiallytheeffectsofC–C tinuouslymaintainingtheCAintheHelmholtzplane.Atthesametime, 2 coupling and hydrocarbon or oxygenated multi-carbon chemicals in order to avoidthe overhigh positive potential during pulse elecselectivity.Thermodynamically,Cu(100)facetwasconducivetoC–C trolysisaffectingthestructureandmorphologyoftheCucatalyst,a coupling,whichwasverifiedbypreviouswork49,50.Consequently,we specific asymmetric pulse electrolysis procedure was designed, i.e., constructedaCu(100)catalystmodelwithandwithoutaCAmolecule −1.6V for 15min, then rapidly switching to 0.1V for 5min (Fig. 6a, adsorbedonthesurface(denotedasCu(100)-CAandCu(100),SupSupplementaryFig.24).Thiscontinuousdynamicpotentialswitching plementary Data1).</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>*CO was a key intermediate in the synthesis of strategy significantly improved the stability of the reaction system, multi-carbonchemicals,andC–CcouplingstepfollowingthereducallowingthecontinuousandstableelectrosynthesisofC HOHforup 2 5 tionofCO toCOwasusuallyregardedastherate-determiningstep51,52. to 40h.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -952,19 +1334,43 @@
           <t>S0164</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Here, distillation was employed for the 2 5 theΔGofeachstepfrom*OC H toC H andC HOHonCu(100)and separationofC HOHproducedbyCO RR,whichwasduetothefact 2 3 2 4 2 5 2 5 2 Cu(100)-CA were calculated and shown in Fig. 5h, i, corresponding thatthedistillationwascommonlycommercialwayofseparationand modelstructureofreactionintermediateswerealsoshowninFig.5j purification for alcohols.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Calculations suggested that one ton (t) of andSupplementaryFig.21–23.TheΔGofC H formation(−0.43eV)on C HOHproducedbyCO electrolysisusingrenewablewindenergyas 2 4 2 5 2 bareCu(100)waslowerthantheformationof*OC H (0.14eV),verthedrivingforceemitted1.2tofCO accordingly,whichsubstantially 2 4 2 ifyingthecleavageofC–ObondwasmorefavorablethanCu–Obond, lower than that of conventional coal-to-CHOH and biomass-to2 5 resultingintheformationofC H insteadofC HOH.Onthesurfaceof C HOHapproacheswithemissionvaluesof7.6and3.9t /t , 2 4 2 5 2 5 CO2 C2H5OH Cu(100)-CA, the ΔG of C H formation exhibited major uphill to respectively(Fig.6g,SupplementaryNote1,SupplementaryTable2)59. 2 4 −0.24eV, whereas the ΔG of *OC H formation was downhill to Additionally, under current TEA analysis, the system of CO 2 4 2 NatureCommunications|( 2025)1 6:8390 8</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -986,19 +1392,47 @@
           <t>S0165</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Therefore, our system consists of three classes of sites with expanded Cu@Ag distances compared to Cu@Cu potentiallyactivesitesduringCORR:Ag/AgCu/Cu. and, most importantly, differences in the predominant CO 2 To further understand how the structural/chemical rearbinding motifs.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>DFT calculations of our previous study rangementsinfluencethereactionmechanism,itisusefulto showed that an expanded Cu lattice increases the binding correlate such changes with the formation and stability of energies for the intermediates of CORR (e.g., *CO on 2 different intermediates during CORR.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>The production of Cu).[9c] Additionally, Ag incorporation in Cu weakens the 2 CO increased at lower overpotentials with increasing Ag bindingenergies of the reduced aldehyde intermediates and content in the samples.[19] It has been suggested that *CO, inhibitstheirfurtherreductiontoethanoland1-propanolas which is a key intermediate for the C@C coupling mechademonstrated in a recent DFT study.[22] However, the nism,[19] might couple with *CH[20] to form the *CHCHO structural analysis of the catalysts showed that the surface x 2 intermediate, which plays a central role in the formation of partially consists of Cu/Ag areas, which also leads to the C liquid products.[21] The *CHCHO intermediate can be formationofethanoland1-propanolattheCusites,sincethey 2+ 2 hydrogenatedto*CHCHOandformacetaldehyde[Eq.(1)] are expected to have higher binding energies for the oxy3 orbefurtherhydrogenatedtoyieldethanol[Eq.(2)]. genated intermediates as compared to the Ag–Cu mixed Angew.Chem.Int.Ed.2021,60,7426–7435 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH www.angewandte.org 7433 15213773, 2021, 13, Downloaded from https://onlinelibrary.wiley.com/doi/10.1002/anie.202017070 by CochraneAustria, Wiley Online Library on [23/05/2026].</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1020,19 +1454,43 @@
           <t>S0166</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Journal of the American Chemical Society pubs.acs.org/JACS Article Previous studies in H-type cells have demonstrated that the presenceofdefects,specificfacets,andgrainboundariesonthe Cu surface promotes the C−C coupling required for C product generation.5−8,45−47 It should be noted not only tha 2 t the pulse electrolysis treatment employed here affects the catalyst morphology, chemical state, and local pH around the activemotifsbutalsothattheoxidativepotentialsmightresult intheoxidationofalcohols,aldehyde,andformatetogenerate more carbonaceousintermediates(including *CO), which are keyintermediatestoC products,particularlyC H .However, 2+ 2 4 thelattereffectwasdiscardedasasignificantcontributortothe selectivity trends obtained, since the enhanced C selectivity 2+ was preserved after the pulse treatment was interrupted and the same sample was subsequently measured under potentiostatic conditions (constant negative applied potential).</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
+          <t>This indicates that irreversible changes in the sample morphology Figure7.(a)Operandosurface-enhancedRamanspectraunderOCP, takingplaceduringthepulsetreatmentaremainlyresponsible potentiostatic operation at −0.7 V, and pulsed conditions with differentE values.DashedlinesrepresenttheRamanbandsofCuO for the improved C 2+ selectivity detected.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1054,19 +1512,43 @@
           <t>S0167</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Based on the analysis above, we elucidated how the 2 4 compared to the protonation of α-C to form *CH CHO intergeometry of C–C active sites affects the bifurcation pathway, 3 mediate.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Conversely, s-sq site shows strong thermodynamic resulting in the difference of the selectivity for C 2+ products. tendency for further hydrogenation, thus inhibiting the C H Furthermore,wecanproposethatthekeytogeneratingethanolis 2 4 pathwayandmeanwhilepromotingalcoholsproduction(Fig.3c). that square-like sites coupled with low coordinated sites, where Fig.3Identificationofproduct-specificactivesites.Energyprofiletoformethylene(blueline)andethanol(orangeline)foraplanar-squaresite,b convex-squaresite,andcstep-squaresite.dBlue:TherelationshipbetweenthebondlengthofC–OinadsorbedCH CHOandthedifferenceofGibbs-free 2 reactionenergyofC–Oscission(ΔG(C–O))andhydrogenation(ΔG(+H)).Orange:TherelationshipbetweenthebondlengthofC–Oinadsorbed CH CHOandtheICOHPofC–Obond.eGeneralcoordinationnumberandadsorptionenergyof*CH CHOonthesethreeactivesites.fAdsorptionenergy 2 3 of*Oonthesethreeactivesites. 4 NATURECOMMUNICATIONS| (2021) 12:395 |https://doi.org/10.1038/s41467-020-20615-0|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1088,19 +1570,47 @@
           <t>S0168</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-20615-0 created by two flat (111) planes with 60° lattice orientation difTheseresultssuggestthatp-sqandcv-sqsitesareresponsiblefor ference. s-sq sites are similar to Cu(S)-[n(111)×(100)] step sites generating ethylene while s-sq favors the alcohols production. where(100)stepsareintroducedto(111)basalplane.Whilecc-sq Interestingly, we found that the tendency to produce ethylene and cv-sq are formed by rotation and then splicing of two (111) or alcohols can be simply predicted by the C–O bond length of planes.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>In order to explore C–C coupling more accurately, we *CH CHO.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>The shortest C–O bond length (1.296Å) is in 2 abstracted these four surface sites into small slab models for *CH CHO on s-sq site, followed by that on p-sq and cv-sq sites 2 accurate density functional theory (DFT) calculations (Fig. 2d), (1.315Å and 1.322Å).</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,19 +1632,47 @@
           <t>S0169</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>In order to explore C–C coupling more accurately, we *CH CHO.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>The shortest C–O bond length (1.296Å) is in 2 abstracted these four surface sites into small slab models for *CH CHO on s-sq site, followed by that on p-sq and cv-sq sites 2 accurate density functional theory (DFT) calculations (Fig. 2d), (1.315Å and 1.322Å).</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>To further quantitatively evaluate the which are expected to have similar chemical properties to the strength of the bond, we conducted the integrated crystal orbital selectivesitesfromtheMDmodels(MethodsandSupplementary Hamilton population (ICOHP) analysis of C–O bond (Fig. 3d).</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1156,27 +1694,51 @@
           <t>S0170</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>One possible mankind1,2.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Copper and copper-based compounds have been well reasonliesinthehighlyreductiveenvironmentatthecathodesurface, reckonedhighlyeffectiveinproducingdeeplyreducedmulti-electron makingtheoxygenicintermediatesdifficulttostay,especiallybeyond products,owningtothesuitableintermediatesbindingenergeticsthat thepotentialsofC–Ccoupling.Exquisitecatalystdesignandfabricaallowserialreactioncascades3,4.Amongthediversereactionproducts tion, aiming to tune individual intermediate binding and break the 1SoochowInstituteforEnergyandMaterialsInnovations,CollegeofEnergy,KeyLaboratoryofAdvancedCarbonMaterialsandWearableEnergyTechnologies ofJiangsuProvince,SoochowUniversity,215006Suzhou,P.R.China.2JiangsuKeyLaboratoryofAdvancedNegativeCarbonTechnologies,Soochow MunicipalLaboratoryforLowCarbonTechnologiesandIndustries,SoochowUniversity,215123Suzhou,Jiangsu,P.R.China.3SchoolofChemicalEngineering andAdvancedMaterials,TheUniversityofAdelaide,Adelaide,SA5005,Australia.4InstituteofFunctionalNano&amp;SoftMaterials(FUNSOM),JiangsuKey LaboratoryforCarbon-BasedFunctionalMaterials&amp;Devices,SoochowUniversity,215123Suzhou,China.5Theseauthorscontributedequally:BaiyuYang, LingChen. e-mail:zdeng@suda.edu.cn;yan.jiao@adelaide.edu.au;ypeng@suda.edu.cn NatureCommunications|( 2022)1 3:5122 1 ;,:)(0987654321 ;,:)(0987654321</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>P5:OCHO</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1198,19 +1760,47 @@
           <t>S0171</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>To further study the electronic still needed to understand the structure-activity relationship structure of the catalysis, Cu K-edge X-ray absorption spectro- (SAR) and efficient conversion CO to multi-carbon products scopy, X-ray photoelectron spectroscopy (XPS) and soft-X-ray 2 especially for high economy asymmetric C 2+ products (e.g., absorption spectroscopy (XAS) were carried out as shown in ethanol).</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Therefore, the design of catalysts that selectively proFig.1e–gandiandSupplementaryFig.5.TheCu2p XPSfitting 3/2 duceethanol viaelectrochemical CO RRwere supposed tofocus curves revealed that Cu was mainly +1 and +2 valence in Cu/ 2 onminimizingthreecompetingreactionpathwayswhichreduced N C26,27.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The Cu L3M45M45 Auger electron spectroscopy 0.14 thefaradaic efficiency(FE)ofasymmetricethanol byconsuming (AES) showed no distinct peak around 918.5eV which indicated electronsandprotons,thehydrogenevolutionreaction(HER),C thatnoCu0 existed onthesurface.TheN K-edgepresentedfour 1 product formation (e.g., CH , HCOOH) and other symmetrical obvious resonances (Fig. 1i) assigned peak A , A , and A to 4 1 2 3 C product formation (e.g., ethylene).</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1232,19 +1822,47 @@
           <t>S0172</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>On the contrary, for Cu –CuN , the 3 3 active sites with the applied potential and represents the growth adsorptionoftheHisspontaneousprocess,whiletheadsorption of Cu clusters that may be the active site for the formation of of CO is still non-spontaneous process, illustrating the H 2 ethanol according the results of operando XAS analysis.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>The adsorption is advantage state for the competing reaction. reaction pathway of CO RR to CH CH OH for the Cu –CuN Therefore, the larger amounts of H were adsorbed on the 2 3 2 2 3 cluster was investigated combined by the computational hydroCu –CuN sites, which preempted the adsorption sites of CO 3 3 2 gen electrode approach as shown in Fig. 5a, b, Supplementary and reduced the amount of ethanol produced.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>It corresponded Fig. 28, and Supplementary Data 1–1352.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1266,27 +1884,55 @@
           <t>S0173</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>These favorable than that of * CO on Cu surface46.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Therefore, the peaks, indexed to the absorbed * OCCOH and * OC H on these atop 2 5 C–C coupling on dCu O/Ag could be triggered under catalysts, exhibit a ratio value for * OC H / * OCCOH on dCu O/ asymmetry between * CO 2 and 2 * .</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>C 3% HO (or * COH) following the Ag thatissignificantlygreatercomp 2 ar 5 edwiththatfordCu 2 O 2.3% 2 * CO protonationstep.Notably,adsorbed * CHOintermediate and dCu O/Au .</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1308,19 +1954,47 @@
           <t>S0174</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Figure 4 C-C bond formation via a formyl-bicarbonate coupling pathway (with a key intermediate 4).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Reaction energy proles and the corresponding intermediate structures (0 to 7) for the formation of ethanol via the CO RR on the Sn -O3G catalyst.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Extended data Fig. 58 shows the detailed free energy proles for 3 to 5. 2 1 Supplementary Files This is a list of supplementary les associated with this preprint.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1342,19 +2016,47 @@
           <t>S0175</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>40 18 15 30 12 20 9 6 10 3 0 0 40 60 80 100 120 140 160 Accordingly,theeffectofCO masstransportonlocalCO conThelocalCO concentrationcanfurtherinfluencethecoverageof 2 2 2 centration needs to be further studied.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>However, it is difficult to *CO,whichaffectsthereactionpathwaystowardethyleneandethanol. measure local CO concentration in the catalyst layer directly.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>To Thus,in-situATR-SEIRASwasemployedtofurtherevaluatetheimpact 2 investigate the localCO concentration ofdifferentinterfacialwettofinterfacialwettabilityontheadsorptionofintermediates(Fig.3d,e). 2 ability,controlsampleswerepreparedwithdifferentgas–liquid–solid There is a stretching band at ~2070cm−1 on all electrodes, correcontact, enabling in situ measurements with fluorescence electrospondingtothestretchingbandofthelinear-bondCO(CO )ontheCu L chemical spectroscopy (FES) at 100mAcm−2 chronopotentiometry surface43,44.Asforhydrophobic-treatedCuelectrodes,theCO bands L (Fig.3b).ThelocalCO concentrationofallsamplesdecreasestoanew becomemoreclearlydefinedatmoderateoverpotentials(−0.6to1.2V 2 steadystateduringelectrolysis.Asforthethree-phasecontactelecvs.RHE),indicatingalarger*COcoverage.Furthermore,CO bandsare L trode,increasinghydrophobicitycanshortentherelaxationtimeof preferentially observed on hydrophobic-treated Cu surfaces under thelocalCO concentrationandincreaseequilibriumconcentration, more negative potentials, with a wider voltage range of *CO 2 whichcanfacileCO masstransport.ThelocalCO concentrationwill coverage14,45.Theenhanced*COadsorptioncanbeattributedtothe 2 2 return back to the initial equilibrium value after electroreduction highproduction rateofthe accumulationofmore*COona hydro- (SupplementaryFig.30).TherecoveryoflocalCO concentrationon phobicCusurfaceunderahighlocalconcentrationofCO 31.Thedif2 2 the highly hydrophobic interface is faster due to the improved gas ferencein*COcoverageoverawidevoltagerangederivedfromthe diffusion.Theseresultsdemonstratethattheinterfacialcontactstate wettabilityofthecatalystlayerisoneofthekeyfactorsfortheethylene affectstheCO masstransportfromthebulkphasetothecatalyst,thus andethanolpathways. 2 affectingthelocalCO concentrationnearbythecatalyst. 2 The hydrophobic treatment also can promote CO diffusion in Effectofcontrollablewettabilityon*HcoverageviaH Omass 2 COreductionreactions.Thus,itcanbeexcludedthatthelimitedCO transport 2 masstransportatthehydrophilicCuelectrodeisentirelyduetothe As another key intermediate, the *H intermediate on the surface is neutralization of CO with the electrolyte (Fig. 3c, Supplementary convertedfromthebulksolution,whichisaffectedbyH Otransport. 2 2 Fig. 31).</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1376,19 +2078,43 @@
           <t>S0176</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-023-36926-x Accelerating electrochemical CO reduction 2 to multi-carbon products via asymmetric fi intermediate binding at con ned nanointerfaces Received:1October2022 JinZhang1,5,ChenxiGuo2,5,SusuFang 3,XiaotongZhao1,LeLi1,HaoyangJiang1, ZhaoyangLiu1,ZiqiFan1,WeigaoXu 3,JianpingXiao 2,4 &amp;MiaoZhong 1 Accepted:22February2023 ElectrochemicalCO reduction(CO R)toethyleneandethanolenablesthe 2 2 Checkforupdates long-termstorageofrenewableelectricityinvaluablemulti-carbon(C ) 2+ chemicals.However,carbon–carbon(C–C)coupling,therate-determining stepinCO RtoC conversion,haslowefficiencyandpoorstability,especially 2 2+ inacidconditions.Herewefindthat,throughalloyingstrategies,neighbouring binarysitesenableasymmetricCObindingenergiestopromoteCO -to-C 2 2+ electroreductionbeyondthescaling-relation-determinedactivitylimitson single-metalsurfaces.WefabricateexperimentallyaseriesofZnincorporated CucatalyststhatshowincreasedasymmetricCO*bindingandsurfaceCO* coverageforfastC–Ccouplingandtheconsequenthydrogenationunder electrochemicalreductionconditions.Furtheroptimizationofthereaction environmentatnanointerfacessuppresseshydrogenevolutionandimproves CO utilizationunderacidicconditions.Weachieve,asaresult,ahigh31±2% 2 single-passCO -to-C yieldinamild-acidpH4electrolytewith&gt;80%single2 2+ passCO utilizationefficiency.InasingleCO Rflowcellelectrolyzer,werealize 2 2 acombinedperformanceof91±2%C Faradaicefficiencywithnotable 2+ 73±2%ethyleneFaradaicefficiency,31±2%full-cellC energyefficiency,and 2+ 24±1%single-passCO conversionatacommerciallyrelevantcurrentdensity 2 of150mAcm−2over150h.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Owing to rapid population and economic growth as well as ElectrochemicalCO reductionisamild,carbon-neutralroutefor 2 increasedanthropogenicactivities,globalenergy-relatedCO emisthelarge-scaletransformation ofwasteCO intovaluablechemicals 2 2 sionreached31.5billiontonsin20201.Theresultingglobalwarming usingrenewableelectricityandwater2–7.Thisapproachisparticularly andenvironmentalcrisesrequiretherapidimplementationofclean beneficial when targeting highly demanding multicarbon (C ) pro2+ and efficient recycling measures to reduce the global carbon ductssuchasethyleneandethanol8–13.Toachieveapositivenetprefootprint. sentvalueintechno-economicanalysesofCO R,&gt;80%selectivityand 2 1CollegeofEngineeringandAppliedSciences,JiangsuKeyLaboratoryofArtificialFunctionalMaterials,NationalLaboratoryofSolidStateMicrostructures, NanjingUniversity,Nanjing210023,China.2StateKeyLaboratoryofCatalysis,DalianNationalLaboratoryforCleanEnergy,DalianInstituteofChemical Physics,ChineseAcademyofSciences,ZhongshanRoad457,Dalian116023,China.3KeyLaboratoryofMesoscopicChemistry,SchoolofChemistryand ChemicalEngineering,NanjingUniversity,Nanjing210023,China.4UniversityofChineseAcademyofSciences,Beijing100049,China.5Theseauthors contributedequally:JinZhang,ChenxiGuo. e-mail:xiao@dicp.ac.cn;miaozhong@nju.edu.cn NatureCommunications|( 2023)1 4:1298 1 ;,:)(0987654321 ;,:)(0987654321</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1410,19 +2136,47 @@
           <t>S0177</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Wetheorizethatalloyingstrategies,inwhichanenhancermetalis Wecalculatedtheactivationbarriersascriticalkineticparameters introducedintothelow-activitybutrelativelystableCu(111)facets,can forevaluatingtheactivityofC–Ccoupling.Figure1dshowsCO*–CO* createneighbouringbinarysiteshavingasymmetricsurfaceCObindcouplingonCu,CuZn ,andCuZn (211)facets.Thekineticenergyis Cu Zn ing energies to improve C–C coupling beyond the scaling-relationreducedby~0.16eVontheCuZn site.Wecomparedtheactivation Zn determinedactivitylimitationsonsingle-metalsurfaces.Wedevelop energiesforCO*–CO*,CO*–CHO*,andCO*–COH*couplingversusthe anactiveglobal-energy-optimizationdiagramtoidentifytheoptimal correspondinglimitingpotentialsoftherelevantpathsonlow-index routeforC–Ccouplingondifferentactivebinarysitesinelectrolytes Cu, CuZn and CuZn (111), (211), and (100) surfaces (Fig. 1e).</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Cu, Zn underreductionconditions.UsinginsituRamanspectroscopy,elecCuZn211 was identified as the most active site, with a small C–C Zn trochemicalhydrodynamicsimulations,andelectrochemicaloperatcoupling barrier and a low limiting potential (Fig. 1e).</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Microkinetic ing experiments, we determine the key features of intermediate modelling26furthervalidatedtheenhancedactivityoftheCuZnalloy adsorptionandelectrocatalyticenvironmentthatleadtothemarked for CO R to C , with CuZn211 showing the highest theoretical 2 2+ Zn CO RperformancewithimprovedCO utilizationinacidicconditions. activity (Fig. 1f).</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1444,27 +2198,55 @@
           <t>S0178</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>The solvation effects were also examined formingthesimulationsusingtheabovegoverningequations. using explicit models, which validated the results from the implicit Importantly,intheelectro-chaoticsystems,thevertexchaosor model (Supplementary Table 8).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Note that the solvent effect for ionconvectionismainlydeterminedbytheelectrostaticforcesand OCCO*wassimulatedusingpolarisedexplicitwatermodels,forwhich notbythefluidinertia34,43.Theionconcentrationsnearsurfacesare the uncertainty of the adsorption energy has been reported to be mainlygovernedbytheappliedvoltages.Afterafewmicroseconds, negligible20. the concentrations of ions in the 30nm pores reach a quasi-steady state,anorderofmagnitudehigherthanthatontheflatsurfaceorin Energyglobaloptimization the150nmpores.Thenumericalsimulationsshowedthat30nmpores By considering the elementary steps in the simplified reaction netincreasedthepotassiumconcentrationsnearthesurfaces.Asaresult, work, all possible pathways can be enumerated24,25.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The elementary hydrogenevolutionreaction(HER)issuppressed. stepwiththehighestlimitingenergywasdefinedasthelimitingstepin aspecificpathway(r ,r ,andr inSupplementaryFig.3).Thepathway Dataavailability A B C with the lowest limiting energy among all possible pathways was Sourcedatatogeneratefiguresandtablesareavailablefromthecorchosen as the most favoured pathway (red path in Supplementary respondingauthors.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1486,19 +2268,47 @@
           <t>S0179</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The ethanol formation rate shows a minimum CO adsorption and thus the coupling between acetaldehyde between 12.5 and 17.5 mL min−1 of CO flow while the and CO is compromised. propanol formation rate increases significantly, reaching its ■ maximum at 17.5 mL min−1.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>The fact that the production of ASSOCIATED CONTENT ethanolisminimalwhentheproductionofn-propanolreaches * sı Supporting Information its maximum suggests that methylcarbonyl is an intermediate The Supporting Information is available free of charge at fortheformationofbothmolecules.Thistrendisnotobserved https://pubs.acs.org/doi/10.1021/acscatal.3c00190. for ethylene formation (Figure 5a), indicating that methylSEM images of the Cu electrode surface, acetaldehyde carbonyl is not an intermediate in the ethylene pathway. conversion in the absence and in the presence of CO, Finally, our results show that low flow rates are not beneficial and Faradaic efficiency for H and carbon products at as a high local CO concentration is needed to form the key 2 different CO partial pressures (PDF) CO−dimer and the corresponding C intermediates, such as 2 methylcarbonyl.21−23 Recently, Hou et al.32 have showed that ■ the increase in CO coverage, by increasing the CO pressure, AUTHOR INFORMATION favorstheselectivitytowardoxygenates,especiallyacetate,over Corresponding Author ethylene.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In addition to the work of Hou et al., our results in Marc T.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1520,27 +2330,51 @@
           <t>S0180</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41560-024-01633-4 a c 1,2901,4201,605 13CO 2 H 2 O CO 2 D 2 O CO 2 H 2 O 1,305 1,443 2,100 –1.00 V 1,575 –0.95 V –0.90 V 268 354 1,070 1,182 1,320 1,455 –0.85 V 1,200 1,400 1,600 2,045 –0.80 V 275 –0.76 V 358 500 1,000 1,500 2,000 –0.70 V b –0.65 V Assignment N Cu–Cu ν 12C (cm–1) ν 13C (cm–1) ioChem-BD –0.60 V CCO symmetric 6.17 1,184, 1,156, OD-Cu-254 –0.55 V stretching 5.00 1,185 1,158 OD-Cu-297 CCO –0.50 V antisymmetric 5.00 1,323 1,317 OD-Cu-297 stretching –0.40 V C–C stretching 6.17 1,476 1,443 OD-Cu-254 –0.30 V C–O (or C=C) stretching 8.03 1,595 1,543 OD-Cu-263 OCP 900 1,200 1,500 1,800 Raman shift (cm–1) −0.56 V to −0.76 V , the *OCCO intermediate forms on the surface The formation of defects on the Cu surface during CORR, for RHE RHE 2 and evolves to ethylene at −0.76 V .</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Instead, the *OCHCH key interinstance, adatoms or small Cu clusters with low-coordinated Cu atoms, RHE x mediate is detected from −0.85 V , the observed onset potential for has been experimentally observed via electrochemical scanning tunRHE CORR to alcohols.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1562,19 +2396,47 @@
           <t>S0181</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>However, the tandem approach usually leads to NW,diffractionpeaksofbothmetallicCuandAgareclearlyobservable. uncontrolledC-Ccoupling,producingavarietyofC productssuchas The contents of Ag in AgCu NW and AgCu NW were measured by 2+ 1 ethylene,ethanol,andacetatethroughcascadecatalysis.Grätzeletal.35 inductivelycoupledplasmaemissionspectrometer(ICP)andtheresults andYangetal.34suggestedthattheefficient*COspilloverfromAgto aresummarizedinSupplementaryTable2.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Cucouldimprovesethyleneperformance.Qiaoetal.23claimedthat Thesurfacevalencestatesofthe as-synthesizedCu NW,AgCu 1 significantly boosted ethanol production could be achieved by the NWandAgCuNWwereanalyzedbyX-rayphotoelectronspectroscopy tailoredintroductionofAgtooptimizethecoordinatednumberand (XPS).ThesurveyXPSspectrashowagradualincreaseoftheAgpeak oxidationstateofsurfaceCusites.However,duetothecomplexityand withincreasingAgcontent(SupplementaryFig.9andSupplementary diversity of the catalyst’s structure, the underlying mechanism of Table3).Thehigh-resolutionO1sXPSspectrumofCuNW,AgCuNW 1 CO RRtoethylene/ethanolintheCu-Agsystemremainsunclear34,36,37. andAgCuNWexhibitsimilarcharacteristicpeaksat530.5and532.4eV, 2 Recently,therapiddevelopmentofsingle-atomcatalysishasopened whicharerelatedtoadsorbedsurfacehydroxide(OH )andadsorbed ads upnewpossibilitiesforconstructingmodelcatalystswithasymmetric water (H O ), respectively (Supplementary Fig. 10)46.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>As shown in 2 ads catalyticsites38,39.Inparticular,modificationofcopper-basedcatalysts Fig.1fandSupplementaryFig.11,thebindingenergyofAg3ddisplays withsinglemetalatoms,andrationaldesignofcatalystswithdual-or a positive shift from 368.2eV (Ag NW) to 368.4 (AgCu NW) and 1 multi-catalyticsiteshavebeenshownpromisingtoinduceasymmetric 368.3eV(AgCuNW),implyingagraduallydecreasedchargedensityon C-CcouplinginCO RR40–42.However,littleunderstandingaboutthe AgduetoelectrontransferfromAgtoCu47. 2 exactasymmetricC-Ccouplingmechanismisknown.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1596,19 +2458,47 @@
           <t>S0182</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>One-dimensional Cu 2 2+ conventionallyconsideredtoproceedviaacomplexC-Ccoupling nanowires with an average diameter of 45±3nm were imaged by mechanism involving various intermediates such as *COCO, scanningelectronmicroscopy(SEM)andtransmissionelectronmicro- *COCHO, *COCOH, *CH CO, and *OCHCH , etc1,15–25.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Therefore, scopy(TEM)(Fig.1bandSupplementaryFigs.1,2).AsshowninFig.1c, 2 2 regulating the key intermediates involved in the CO RR over theAgCuNWexhibitstypicalcharacteristicsofsupportedcatalyst,with 2 catalytic sites and optimizing their binding energies become criAg nanoparticles distributed as islands on the surface of the Cu NW tical to adjust the C-C coupling pathways towards targeted C (SupplementaryFigs.3,4),andobviousgrainboundariesbetweenAg 2+ products.Nevertheless,manipulationofC-Ccouplingpathwaysis nanoparticles and Cu NW can be clearly observed (Supplementary still highly challenging due to the complexity of the catalytic Fig.4b).Incontrast,AgCuNWdisplayssimilarmicrostructuralfeatures 1 system, the unclear reaction intermediates and the limited to Cu NW (Fig. 1d and Supplementary Figs. 5, 6).</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>High-angle annular mechanisticunderstanding. dark-field scanning transmission electron microscopy(HAADF-STEM), Cu-based materials have been well established as promising energy-dispersive X-ray spectroscopy (EDX) elemental mapping and electrocatalystscapabletoreduceCO tomultipleC products11,26–28. electronmicroscopy-basedatomrecognitionstatistics(EMARS)analysis 2 2+ Till now, a large number of Cu-based tandem catalysts have been on HAADF images of AgCu NW indicate that isolated Ag atoms are 1 developed to realize high selectivity in CO RR to produce C prouniformly distributed on the surface of Cu NW matrix in AgCu NW 2 2+ 1 ducts,primarilyresultingfromtheimprovedmasstransportof*CO (Fig. 1e and Supplementary Figs. 6c, d and 7)44.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1630,19 +2520,47 @@
           <t>S0183</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>The assignments for additional peaks ethanol.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Meanwhile, mass spectrometry (MS) spectra of liquid proobserved in the ATR-SEIRAS spectra at ~2332, ~1265, ~1183 and ducts from CO RR exhibit signals at m/z=45.03 and m/z=46.03, 2 ~1034cm−1aresummarizedinSupplementaryTable10.Comparedto which can be attributed to 12CH 12CH O+ and 13CH 12CH O+ or 3 2 3 2 AgCuNW,ablue-shiftin*CO peakonAgCuNWwasnoticedat 12CH 13CH O+,respectively(Fig.4i)61.Basedonalltheseresults,Fig.4g bridge 1 3 2 variousappliedpotentials,suggestingenhancedbindingstrengthof schematicallyproposesthepathwayofCO RRtoethanoloverAgCu 2 1 *CO on AgCu NW.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Additional new peaks at around 1244cm−1 and NW, where methyl C (-CH ) and methylene C (-CH OH) in ethanol 1 3 2 1083cm−1 were observed on AgCu NW, which can be assigned to originatefrom*COand*HCHOintermediates,respectively. 1 adsorbed*CHOand*COCHOintermediates,respectively(Fig.4e)60.As showninFig.4f,thepeakintensityof*COCHOintermediatewasfound Theoreticalinsightsintothecatalyticmechanism tograduallyincreasewithincreasingappliedcathodicpotentialfrom Densityfunctionaltheory(DFT)calculationswereperformedtogain −0.4to−1.2VvsRHE,whilethepeakintensityof*CHOintermediate insightsintotheunderlyingreactionmechanismsforthedistinctive was correspondingly decreased, suggesting production of *COCHO selectivityofCO electroreductiontoethyleneandethanoloverAgCu 2 intermediatefromasymmetric*CO-*CHOcoupling.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1664,19 +2582,47 @@
           <t>S0184</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Moreover, the surface sulfur vacancies cEreated by subsurface Co-doping help R regulate the optimal distance between dual sites, faciliPtating asymmetric C-C coupling.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Theoretical N calculations combined with in-situ isotopic spectroscopy validate these views, and the branching I pathway for converting *CHCO to *CHC E HO* is captured.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Consequently, in a membrane electrode L C assembly electrolyzer, the optimized Co-Sub-CuS achieves an ethanol Faradaic efficiency of 78.7% I T at a partial current densityR of 550.9 mA cm-2, with stability over 305 h at industrial-level current A density of 700 mA cm-2.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1698,27 +2644,55 @@
           <t>S0185</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-025-63009-w Fig.5|In-situcharacterizationandtheoreticalcalculations.In-situFT-IRspectra *OCH intermediateonCu(100)(left)andCu(100)-CA(right).gDiagramofCA2 3 ofcommercialCuunderCORRinelectrolyte(a)withoutCA,(b)withCA.a.u. dominatedCO-to-CHOHconversionmechanismoverCucatalyst.Gibbsfree 2 2 2 5 arbitraryunits.cSchematicofCO2RRmechanismandpathwayforvarioussingle-/ energydiagramof*OC2H3toC2H4orC2H5OHover(h)Cu(100),(i)Cu(100)-CA. multi-carbonproducts.dΔGdiagramofC–CcouplingonCu(100)andCu(100)-CA. jTheatomicstructureofC–CcouplingandC2H4/C2H5OHformationstateson eCOHPanalysisofC–Obondinginteractionin*OCH intermediateonCu(100) Cu(100)-CA.Colorcode:grey(C),white(H),red(O),orange(Cu). 2 3 (left)andCu(100)-CA(right).fCOHPanalysisofCu–Obondinginteractionin theabsorbancepeaksintherangeof1200to1600wavenumberswere AfterdecouplingtheroleofCAontheselectivityofCO RR,the 2 presentedduetothepresenceofCA,indicatingthattheCAatthesubinteractionofCAattheHelmholtzplanewithH OmoleculesandH O 2 2 nanoreactioninterfaceprofoundlyaffectedtheadsorptionstrength dissociationprocesswerefurtherreal-timeinvestigatedandanalyzed and further conversion of reaction intermediates and governed the byahighlysurfacesensitivein-situRamantechnique43,44.Atthe3000CO RR mechanism.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Specifically, for the system without CA, the 3800cm−1positionoftheRamanspectra,theO–Hstretchingvibration 2 *OCCOH,*OC H intermediatescorrespondingtothesynthesisofC can be decomposed into three types according to Gaussian fitting 2 5 2+ productsandC HOHlocatedat1210and1350cm−1aswellasthe*CHO (SupplementaryFig.17)45,46.Revealedbyexistingfindings43,47,K+inthe 2 5 and*OCH intermediatesassociatedwiththeformationofCH at1480 electrolytewasmorelikelytobespecificallyadsorbedontheelectrode 3 4 and1410cm−1wereclearlydetected40–42.Differently,inthepresenceof surface.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>The K+-coordinated water (denoted as K+ H O) will con2 CA, the *OCCOH and *OC H were extraordinarily stronger in the tinuouslysupplyH Otoelectrodesurfaceaswellasacceleratedthe 2 5 2 intensities and dramatically easier than the formation of *CHO and HERkinetics,whichwasmoresignificantlyyeteffectivelyforHERthan *OCH intermediatesfortheformation ofCH ,distinctlyillustrating theothertwostructuraltypesofH O(2-,4-coordinatedH-bondwater, 3 4 2 that the C HOH and C products werefavorablyformed over the whichweredenotedas2-HBH Oand4-HBH O).Thein-situRaman 2 5 2+ 2 2 developed catalyst.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P2:*CHO</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1740,27 +2714,55 @@
           <t>S0186</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Specifically, for the system without CA, the 3800cm−1positionoftheRamanspectra,theO–Hstretchingvibration 2 *OCCOH,*OC H intermediatescorrespondingtothesynthesisofC can be decomposed into three types according to Gaussian fitting 2 5 2+ productsandC HOHlocatedat1210and1350cm−1aswellasthe*CHO (SupplementaryFig.17)45,46.Revealedbyexistingfindings43,47,K+inthe 2 5 and*OCH intermediatesassociatedwiththeformationofCH at1480 electrolytewasmorelikelytobespecificallyadsorbedontheelectrode 3 4 and1410cm−1wereclearlydetected40–42.Differently,inthepresenceof surface.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>The K+-coordinated water (denoted as K+ H O) will con2 CA, the *OCCOH and *OC H were extraordinarily stronger in the tinuouslysupplyH Otoelectrodesurfaceaswellasacceleratedthe 2 5 2 intensities and dramatically easier than the formation of *CHO and HERkinetics,whichwasmoresignificantlyyeteffectivelyforHERthan *OCH intermediatesfortheformation ofCH ,distinctlyillustrating theothertwostructuraltypesofH O(2-,4-coordinatedH-bondwater, 3 4 2 that the C HOH and C products werefavorablyformed over the whichweredenotedas2-HBH Oand4-HBH O).Thein-situRaman 2 5 2+ 2 2 developed catalyst.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>In consequence, the CA dominated and had a spectraresultsexhibitedthattheproportionsofK+H OoverCucat2 determinedeffectonthechangeinCO RRselectivityonCucatalyst,in alystincreasedfrom6.6%to12.3%asthepotentialdecreasedfrom0to 2 whichthekey*COintermediatewasstabilized,resultinginafavored −1VintheelectrolytewithoutCA,aswellasanincreasefrom6.8%to C–C coupling kinetics and restricted directed *CO hydrogenation 10.7%intheelectrolytewithCAwaspresented(SupplementaryFig.18). process,ultimatelypromotedtheC productformationandinhibited ComparedwiththatoftheelectrolytewithoutCA,theproportionofK+ 2+ themethanation(Fig.5c).</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P2:*CHO</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1782,19 +2784,47 @@
           <t>S0187</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>*CO was a key intermediate in the synthesis of strategy significantly improved the stability of the reaction system, multi-carbonchemicals,andC–CcouplingstepfollowingthereducallowingthecontinuousandstableelectrosynthesisofC HOHforup 2 5 tionofCO toCOwasusuallyregardedastherate-determiningstep51,52. to 40h.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>As a sharp comparison, the FE was significantly 2 C2H5OH Therefore,theGibbsfreeenergy(ΔG)oftheC–Ccouplingstepcordecreased to less than 40% after 5h reaction in a constant static respondingtoformthekeyOC**COintermediatewascalculated,where electrolysis(Fig.6b).Bycarryingouttheasymmetricpulseelectrolysis, thevalueof ΔGonCu(100)-CAwas0.51eV,significantlylowerthan thedecayrateofFE decreaseddramatically(Fig.6c).Also,the C2H5OH that on the Cu(100) (1.75eV) (Fig. 5d).</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>This illustrated that the CA XRDpatternsofCACuafterapplyingconstantandpulseelectrolysis molecule was able to enhance the *CO stability indeed, thereby processes illustrated that the valence structure of the catalyst increasingthechances ofC–Ccoupling.Itwas wellknownthatthe remained unchanged (Fig. 6d).</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1816,19 +2846,47 @@
           <t>S0188</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(NCs) with well-ordered (100) facets have been shown to lead to an increase in the selectivity toward ethylene, while Introduction suppressingmethaneproduction.[5e,8] A promising way to further improve the catalystQs Inthequestfordevelopingasustainableenergyeconomy, performanceandselectivityistheintroductionofasecondary the electrochemical reduction of carbon dioxide (CORR) metal.[9]RecentstudiesofCu–Agbimetallicsystemsshowed 2 into value-added chemicals and fuels offers the potential to enhancedselectivityforC products.Inparticular,aphase2+ close the anthropogenic carbon cycle and store renewable blendedAg-CuOcatalysthadathreetimeshigherFaradaic 2 (wind,solar,hydro)energyintochemicalbonds.[1]Ithasbeen efficiency (FE) toward ethanol than Ag-free CuO, but 2 therefore of particular interest to develop efficient and sufferedfromlowactivity(jj j&lt;1mA).[10]Additionally, ethanol selective electrocatalysts, which reduce the reaction overAg-coveredCuOnanowirespreparedviaagalvanicreplace2 potential and steer the reaction toward hydrocarbons and ment reaction enabled a 1.4times higher current density multicarbon oxygenates (C ).</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>The selective generation of toward ethylene production as compared to pure CuO 2+ 2 liquidproductssuchasethanol,1-propanol,andacetaldehyde nanowires.[11] Furthermore, CuAg surface alloys have been is highly desirable due to their high energy densities and foundtobemoreselectivefortheformationofmulti-carbon advantages for storage/transport as compared to gaseous products than pure copper.[12] The facilitated yield of C 2+ products.[2] products in the bimetallic system is usually linked to the suppression of HER due to the enhanced coverage of *CO adsorbates as compared to *H,[12b] and the diffusion of CO [*] A.Herzog,Dr.A.Bergmann,Dr.H.S.Jeon,Dr.J.Timoshenko, from Ag sites to Cu sites that enables C@C coupling (CO Dr.S.Kfhl,C.Rettenmaier,M.LopezLuna,F.T.Haase, spillover).[10,11] Note here that a short diffusion path of CO Prof.Dr.B.RoldanCuenya DepartmentofInterfaceScience and therefore a homogeneous distribution of Cu and Ag at Fritz-HaberInstituteoftheMax-PlanckSociety the surface of the catalyst are essential for an effective CO Faradayweg4–6,14195Berlin(Germany) spillover.[10,12b]Nonetheless,althoughthespatialarrangement E-mail:roldan@fhi-berlin.mpg.de ofCuandAginthesestudiesseemstoplayakeyroleforthe SupportinginformationandtheORCIDidentificationnumber(s)for differentCORRselectivitytrendsobtained,thekeyparamtheauthor(s)ofthisarticlecanbefoundunder: 2 eters for achieving an optimal synergy in Cu–Ag bimetallic https://doi.org/10.1002/anie.202017070. systems are still unknown.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In particular, open questions still T2021TheAuthors.AngewandteChemieInternationalEdition remain on the composition and structure of the most active publishedbyWiley-VCHGmbH.Thisisanopenaccessarticleunder and C -selective systems under operando CORR condithetermsoftheCreativeCommonsAttributionLicense,which 2+ 2 permitsuse,distributionandreproductioninanymedium,provided tions,includingthestabilityofCu 2 O,whichmightbemodified theoriginalworkisproperlycited. byintroducingAg.[13] 7426 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH Angew.Chem.Int.Ed.2021,60,7426–7435</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1850,19 +2908,47 @@
           <t>S0189</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>During CO 2 RR, Cu 2 O is partially [Eq.(3)]and1-propanol[Eq.(4)]canbeformed. reduced to metallic Cu, while the contribution of CuO vanishes.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>In fact, the operando XANES data evidenced the *CHCHOþCOþ2Hþþ2e@þHO! 3 2 ð3Þ incompletereductionofCu 2 Oinallsamplesafterfivehours *CH 3 CH 2 CHOþH 2 O!CH 3 CH 2 CHO ofCORR(upto30%ofCuOremainedinthe3-Ag/CuO 2 2 2 sample).However,wedidnotfindacorrelationbetweenthe *CHCHCHOþ2Hþþ2e@!1-CHOH ð4Þ 3 2 3 7 content of CuO (in the bulk, XAS data) and the increased 2 selectivityforC liquidproducts,whichmightbeduetothe On Cu surfaces, acetaldehyde and propionaldehyde are 2+ completereduction(XPS,SERS)ofthesurfaceCuOspecies usually hydrogenated to ethanol, and 1-propanol is only 2 tometallicCuduringCORR. detectedwithFE&amp;1%,asseenfortheCuONCs.Therefore, 2 2 Since the fraction of Ag in the near-surface is low wecanrelatetheenhancementofthetwoaldehydeselectiv- (&lt;11at%),intermixingisplausiblealthoughaprecisedeterities to the dispersion of the Ag atoms/small clusters on the mination of the Ag/Cu ratio in the AgCu regions is not CusurfaceduringCORR,whichinduceslocallystrainedCu x 1@x 2 possible.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Therefore, our system consists of three classes of sites with expanded Cu@Ag distances compared to Cu@Cu potentiallyactivesitesduringCORR:Ag/AgCu/Cu. and, most importantly, differences in the predominant CO 2 To further understand how the structural/chemical rearbinding motifs.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1884,27 +2970,55 @@
           <t>S0190</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Not surprisingly, step sites, where one atomic height of (111) step is introduced these square sites can efficiently stabilize the *COCO interintoseveralatomicrowsof(111)terrace.Moreover,afewdefects mediate as well.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Two disparate scaling relationship can be likegrainboundariesandvacanciesexist(SupplementaryFig.13). obtained between the average adsorption energy of two binding Up to now, authentic OD-Cu surface structures are obtained *CO (E(CO)) and coupled intermediate *COCO (E(COCO)) on based on NN-MD simulation of the whole reduction process. the non-square sites and square sites.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moreover, these two relaToimprovetheactivityandselectivityforC 2+productsofthe tionshipsalmostsharethesameslopebuthavea0.34eVintercept catalyst, it is crucial to understand the nature of the active sites difference.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1926,19 +3040,47 @@
           <t>S0191</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>27</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>López, B.R.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Cuenya, Revealing the CO Coverage-Driven C–C Coupling Mechanism for Electrochemical CO2 Reduction on Cu2O Nanocubes via Operando Raman Spectroscopy, ACS Catalysis. 11 (2021) 7694–7701. https://doi.org/10.1021/acscatal.1c01478. [44] H.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>An, L.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1960,19 +3102,47 @@
           <t>S0192</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Thein situ inCO RR. 2 2 XASspectraofOct-2CualsotestifythereductionofCu2+toCu0under To elucidate the synergy from the Cu clusters and partially negativebias(Fig.3g,j).At−1.5V,boththespectralfeaturesofXANES reducedHex-2Cu-Ocomplexesinyieldingmulti-carbonproducts,we andFT-EXAFSwellmatchthoseofthecopperfoilwithoutdiscernsoaked the Hex-2Cu-O electrode in ethanol to remove the organic able Cu–N signals, further supporting the view that Cu clusters phaseafterCO RRat−1.2V.Asaresult,thecatalystremainedonthe 2 dominate the post-electrolytic Cu species, which coincides earlier electrodeshouldcomprisemajorlyCuclusterssupportedonKB,as XPSobservations. evidenced by EDXimages before and after soaking (Supplementary SimilarstructuralevolutionofHex-2Cu-Owiththeemergenceof Figs. 30, 31).</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Elemental analysis further shows that the Cu clusters CuclustersduringCO RRwasalsowitnessedbyTime-lapseXAFSata remainedontheelectrodeaccountfor∼82%oftheoriginalCucon2 constantpotentialof−1.2V(SupplementaryFig.25).Injust8min,Cu tent, and that the N content isnotably reduced after soaking (Supcentersinthecomplexwerealreadypartiallyreduced,aswitnessedby plementaryTable5).InthesubsequentretestingofCO RR,theFEof 2 thecoexistenceofCu0andCu–N/OspeciesinboththeXANESandFTmulti-carbonproductsat−1.2Vdecreasesfrom66.2%fortheoriginal EXAFSspectra.After24min,thewholecatalystsystemwasstabilized, catalystto22.1%,inwhichethanolandn-propanolaccountforonly withsimilarCuoxidationandcoordinationstatestilltheendofthe 8.8%and8.2%,respectively.Meanwhile,thetotalefficiencyofC pro1 test.ItisthussurmisedthatmetallicCureducedfromorganometallic ducts(includingformate,COandmethanol)increasesfrom16.3%to precursorsmightimposeself-constraintonparticlegrowthduetothe 40.3%(SupplementaryFig.32).Thisresultissomehowsimilartothe ligand tethering effect and catalyst-support interaction, which have productdistributionobservedonOct-2Cu,whichformscopperclusbeen demonstrated in previous literature reports4,33,34, and further ters and fragmented ligands during electrolysis.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Collectively, these confirmed here by plotting the potential-dependent Cu–Cu CNs observationshelptojustifytheroleofthepartiallyreducedHex-2Cu-O revealingtheslow-downofparticlegrowthwithincreasingbias(SupincontributingtobothC andalcoholproduction.Toreinforcethis 2+ plementaryFig.26).Collectively,ourcomprehensivecharacterizations pointofview,wefurthercastedthesolutefromthesoakingsolution aboveshouldhelptorationalizethegreatelectrocatalyticactivityand backontotheelectrode(SupplementaryFig.33)andobservedthatthe stabilityofHex-2Cu-OaswitnessedinFig.2d. alcoholproductionwaspartiallyrestored.Comparedtotheethanolsoakedelectrode,theregeneratedhybridcatalystcomprisingthecastMechanisticinsightsintothehighC 2+andalcoholproduction back organic phase and Cu clusters is able to augment the FEs of OurchoiceofHex-2Cu-O,Hex-2Cu-2Oand Oct-2CuastheCO RR oxygenates and hydrocarbons atall applied potentialsfrom −1.0to 2 catalysts offers a paradigm for illustrating the correlation of −1.4V(Fig.4a,b).Thesepost-mortemtreatmentsstronglysupportthe structure-property-performance.Forthetwobicentrichexaphyrin interplaybetweenCuclustersandpartiallyreducedHex-2Cu-Oligands complexes, although all copper ions are coordinated to three tosynergisticallypromoteC alcoholproduction. 2+ nitrogen and one oxygen, the geometry and symmetry of the In situ attenuated total reflection surface-enhanced infrared coordinationspheresarequitedifferent.Thesharedoxygenatom absorption spectroscopy (ATR-SEIRAS) was employed to probe the in Hex-2Cu-O and the intramolecular tension from the gabled intermediates associated with multi-carbon alcohol production on structure make the complex less thermodynamically stable, and Hex-2Cu-O (Fig. 4c).</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1994,27 +3164,55 @@
           <t>S0193</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Here we dependent variations in activity and selectivity and reproduces 2 4 observe that OCH CH * is a stable intermediate along the reacseveral key characteristics in experimental observations: 2 2 tion coordinates between two TSs, thus demonstrating the disjointed nature of the reaction OCHCH *+H ++e − → ● When compared to methane, larger shifts in onset O*+C H (g) (Supplementary Fig. 7).</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>In sha 2 rp contrast to the potentials are observed for all C 2 species by varying the 2 4 pH.ThiscanbeattributedtothedifferenceinPETnumber extremely high barriers of directly producing ethylene from OCHCH *, reducing OCHCH * to either acetaldehyde or vinyl (relative to CO) for the rate-determining steps (RDSs) of 2 2 dominant C and C pathways at low overpotentials, i.e., alcohol is almost spontaneous at reducing conditions (Fig. 2g). 2 1 OCCO-Hprotonation forC andCOH-Hprotonationfor Vinyl alcohol is unstable in an aqueous solution at room tem2 perature and ultimately isomerizes to acetaldehyde36.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Once C 1 .Thisinsighthasbeendescribedindetailinourprevious work35. acetaldehydeisformed,ethanolhasbeenexperimentallyvalidated as the only further reduced C product22,37.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2036,19 +3234,47 @@
           <t>S0194</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>We will discuss the potential and 2 pH dependencies in more details later. acetate generation.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Stronger nucleophilicity of hydroxide anions − (OH ) than water further favors the reaction between ethenone We also note that the larger discrepancy in predicting acetate andOH − underhighalkalineconditions6,8,16.Theincorporation production at alkaline condition could be attributed to the ofsolventoxygenfromeitherwaterorOH − isalsosupportedby additional pathway of nucleophilic reaction between OH − and 18Oisotopelabelingexperiments8,16.Onceacetateisformed,the ethenone or surface carbonyl compounds such as CCO* and electrostatic repulsion between the negatively charged electrode CHCO*39.Furthermore,studiesthatattempttodetermineofthe and this anion species, will prevent the acetate from further Tafel slopes for CO R are often based on the RDS—through (2) reduction.ReducingCH 2 CO*towardacetaldehyde/ethanolisthe (cid:1) e 2 ð : n 3k þ B β T Þ ,wherek B istheBoltzmannconstant,Tthetemperature, relevant process competing with acetate formation, which, howetheelementarycharge,nthePETnumberbeforetheRDS,andβ ever, has hardly been investigated28.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Protonation of CH 2 CO* the charge-transfer coefficient of the RDS25,40—we note that the results in surface species CH CO*, OCHCH *, and CH COH*, 3 2 2 RDS approach of determining Tafel slopes is valid only for respectively, all of which tends to be further reduced to C Oxys 2 analyzing the total rate of CO/CO consumption or C /C (Supplementary Figs. 9 and 10).</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2070,27 +3296,55 @@
           <t>S0195</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Thus, the mechanism exploration of lowdevelop the architectural blueprint ofcatalysts and electrolytic syscoordinatedCu/Cu Oonstabilizing*COandoxyhydrocarbonsinter2 temsforpreservingtheoxidationstateandbolsteringtheCO permediatesissignificant. 2 formance of copper-based catalysts, including but not limited to Herein, we demonstrated a low-coordinated Cu/Cu O 2 elemental doping6, interface engineering7,8, intermediate Mott–Schottky catalyst with an enhanced rectifying interface (Cu / L confinement9, and pulse CO electrolysis (P-eCO R owing the Cu O).Thiscatalystadjuststheelectrondensitiesthroughinterfacial 2 2 2 straightforwardandreadilyadjustablemeansofmanipulatinganodic charge exchange, leveraging the difference in Cu and Cu O work 2 potentialsforfacilitatingtheformationofCuoxidespecies)10,11.Espefunctions,whichcaneffectivelyformbondsbetween*COandoxyhycially,theMott−Schottkycatalystpossessestheremarkableabilityto drocarbons under CER conditions.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Furthermore, Cu /Cu O catalyst L 2 hinder the accumulation of electrons, thereby safeguarding the generatedhighlyselectivecatalyticsitesforthecouplingreactionof integrityofCu–Obonds,whilesimultaneouslyenablingswiftelectron *CO–COHandhydrogenationofC H O*intermediatetoC alcohols. 2 2 2+ transfercourtesyofitsbuilt-inelectricfield12,13.Therefore,itnecessiChlorine-dopedcuprousoxide(Cl–Cu O)andpureCu Owereselec2 2 tatestheemploymentofintricatecatalystconfigurationandfabricated as the precursors and electrochemically reconstructed to tiontechniquestoelevatetherectifyinginterfaceeffectsofCu/Cu O unsaturated-coordinate Cu /Cu O and pure Cu /Cu O.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>The low2 L 2 P 2 forthepurposeofbondingoxyhydrocarbons. coordinated Cu /Cu O achieved a C alcohols faradic efficiency L 2 2+ Severalstrategiescanimprovetheselectivityofoxyhydrocarbons (FE )of64.15±1.92%withthecorrespondingenergyefficiencyof alcohols inCER,includingthehighconcentrationoflocal*COaroundtheactive ~39.32%.Inaddition,astableC alcoholsfaradaicefficiencyof&gt;50% 2+ sites14,15,dopingmodificationofcoppercatalystswithheteroatoms16,17, was also obtained during a continuous 50h chronopotentiometry building of crystal defects and low coordination of copper12,18,19. experiment.Ourresearchprovidesaplatformfortherationaldesign Effectively, the coverage of *CO can be facilitated on the lowof low-coordinated Cu–Cu O Mott–Schottky catalysts and analyzes 2 coordinatedCusitesofoxide-derivedCu,leadingtoitssubsequent thekeyelementsforefficientsynthesisofC alcohols. 2+ hydrogenationinto*COH,whichisessentialforthecouplingofOC −COH20,21.Forexample,LianggroupreportedafragmentedCucatalyst Results withabundantlow-coordinatedsitesbyelectrochemicalreconstrucSynthesisandcharacterizationofCu L /Cu 2 Onanoparticles tion ofB-dopedCu O,whichexhibited aC products faradaiceffiThe Cu /Cu O catalysts were synthesized using a simple electro2 2+ L 2 ciencyof77.8%at300mAcm−2(seeref.19).Theoreticalcomputations chemical reconstruction strategy on Cl–Cu O nanoparticles (see 2 havedemonstratedthatthe*CObindingscouldbestrengthenedon detailsin“Methods”,SupplementaryFigs.1–4).TheCu /Cu Ocatalysts L 2 low-coordinated copper sites and prefer to coupling with *COH are designed to function as a Mott–Schottky catalyst of Cu/Cu O, 2 insteadof*COdimerization22.Moreover,theincorporationofhalide which generates enhanced rectifying interfaces between electronspecies and the creation of oxygen vacancy also contribute to the deficientmetalandelectron-richregionbecauseofthedifferencein formationoflow-coordinatedmetalandthecontrolledgenerationof work function (Fig. 1A).</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>P3:CO-COH; P3:CO–COH</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2112,27 +3366,55 @@
           <t>S0196</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Furthermore, Cu /Cu O catalyst L 2 hinder the accumulation of electrons, thereby safeguarding the generatedhighlyselectivecatalyticsitesforthecouplingreactionof integrityofCu–Obonds,whilesimultaneouslyenablingswiftelectron *CO–COHandhydrogenationofC H O*intermediatetoC alcohols. 2 2 2+ transfercourtesyofitsbuilt-inelectricfield12,13.Therefore,itnecessiChlorine-dopedcuprousoxide(Cl–Cu O)andpureCu Owereselec2 2 tatestheemploymentofintricatecatalystconfigurationandfabricated as the precursors and electrochemically reconstructed to tiontechniquestoelevatetherectifyinginterfaceeffectsofCu/Cu O unsaturated-coordinate Cu /Cu O and pure Cu /Cu O.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>The low2 L 2 P 2 forthepurposeofbondingoxyhydrocarbons. coordinated Cu /Cu O achieved a C alcohols faradic efficiency L 2 2+ Severalstrategiescanimprovetheselectivityofoxyhydrocarbons (FE )of64.15±1.92%withthecorrespondingenergyefficiencyof alcohols inCER,includingthehighconcentrationoflocal*COaroundtheactive ~39.32%.Inaddition,astableC alcoholsfaradaicefficiencyof&gt;50% 2+ sites14,15,dopingmodificationofcoppercatalystswithheteroatoms16,17, was also obtained during a continuous 50h chronopotentiometry building of crystal defects and low coordination of copper12,18,19. experiment.Ourresearchprovidesaplatformfortherationaldesign Effectively, the coverage of *CO can be facilitated on the lowof low-coordinated Cu–Cu O Mott–Schottky catalysts and analyzes 2 coordinatedCusitesofoxide-derivedCu,leadingtoitssubsequent thekeyelementsforefficientsynthesisofC alcohols. 2+ hydrogenationinto*COH,whichisessentialforthecouplingofOC −COH20,21.Forexample,LianggroupreportedafragmentedCucatalyst Results withabundantlow-coordinatedsitesbyelectrochemicalreconstrucSynthesisandcharacterizationofCu L /Cu 2 Onanoparticles tion ofB-dopedCu O,whichexhibited aC products faradaiceffiThe Cu /Cu O catalysts were synthesized using a simple electro2 2+ L 2 ciencyof77.8%at300mAcm−2(seeref.19).Theoreticalcomputations chemical reconstruction strategy on Cl–Cu O nanoparticles (see 2 havedemonstratedthatthe*CObindingscouldbestrengthenedon detailsin“Methods”,SupplementaryFigs.1–4).TheCu /Cu Ocatalysts L 2 low-coordinated copper sites and prefer to coupling with *COH are designed to function as a Mott–Schottky catalyst of Cu/Cu O, 2 insteadof*COdimerization22.Moreover,theincorporationofhalide which generates enhanced rectifying interfaces between electronspecies and the creation of oxygen vacancy also contribute to the deficientmetalandelectron-richregionbecauseofthedifferencein formationoflow-coordinatedmetalandthecontrolledgenerationof work function (Fig. 1A).</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>The rectifying interface effect of Cu–Cu O 2 intermediates23,24.Sunandco-workerintervenedthebehavioroflowMott–Schottky catalyst adjusts the electronic densities through coordinationchlorideion(Cl−)adsorptiononthesurfaceofasilver interfacial charge exchange, resulting in reduced adsorption resishollowfiber(AgHF)electrodein3MKClelectrolyte,whichresultedin tanceforintermediatesThiseffectalsoleadstohighercatalyticperthe high concentration of *CO on low-coordination Ag–Cl state for formance due to the electronic perturbation at both sides of the CER25.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization; P3:*COH</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2154,19 +3436,47 @@
           <t>S0197</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RHE with a current density of −14.4mA/cm −2 in K-edge XANES spectra of the Cu/N C together with the 0.14 0.1M KHCO electrolyte.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Moreover, it exhibited superb longreferencesofCuO,Cu OandCufoil.Theabsorptionedgeofthe 3 2 termCO electroreductiondurabilityover10h.Thewell-defined Cu/N C was between the Cu O and CuO, indicating that the 2 0.14 2 self-reconstructionfortheactivesitesofCu/N Calsofacilitate oxidationstateofthecopperspeciesisintheintermediatevalence 0.14 the in-depth mechanistic understandings from complementary statebetween+1and+2.ThefeatureofXANESat8986eVand Operando Spectroscopy (XAS, XPS and FTIR), XANES simula8997eVforCu/N CresembledthemixturedominatedbyCuO 0.14 tionsandtheoreticalcalculationstopresenttheatomicstructurewith a little contribution by Cu + or Cu0 complex.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The Fourieractivity relationship between the ethanol selectivity and in situ transformed (FT) k3-weighted EXAFS oscillation in Fig. 1f also dynamic structure (local structure, electronic structure and the showedthedisappearanceofthefeatureforCu–CuinRspacein adsorbed intermediates), that would benefit the recognition for Cu/N Cwithsimultaneousappearanceofthepeakat1.5Åfor 0.14 the CO RR process.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2188,19 +3498,47 @@
           <t>S0198</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RHE.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Three Cu atoms chemically bonded to To further reveal the key adsorbed intermediates in the eachotherwiththeCu–Cucoordinationnumberof2andoneCu catalyticreaction,wecarriedoutSynchrotronradiationoperando atom bonded to three graphite-like N, forming the Cu –CuN Fourier-transform infrared spectroscopy (SR-FTIRS).</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
+          <t>No 2 3 moiety,asshowninFig.3f.SuchCu moietieswhicharesimilar obvious absorption band was observed on scanning the applied tocopperclusters44havegeometricsh 3 apesofequilateraltriangles, potential ranging from −0.1V to −0.7V vs.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2222,27 +3560,55 @@
           <t>S0199</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>This Fig. 2b.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>CO molecules interact with two exposed Cu atoms, result suggested the rate-determining steps (RDS) altered when 2 respectively, forming coadsorbed (*OCHO+*OCHO) (State 3). thepotentialatdecreasedto−1.2Vvs.RHE,combiningtheFTIR One adsorbed *OCHO was firstly reduced to form *CH +* results in Fig. 4d.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>To further analysis why RDS changed during 3 OCHO (State 9), and then the other *OCHO was reduced to the reaction, the different charge density for Cu -CuN (with/ 2 3 construct*CH +*OCH (State12),thatwentthroughtheC–C without CH * ) and Cu -CuN (with/without CH * ) was 3 2 3 3 3 3 Fig.5DFTcalculationsofCO RRactivity.aReactionprogressofCO toCH CH OHontheCu –CuN at0Vand−0.501Vappliedpotential.The* 2 2 3 2 2 3 showedthereactionsite.Thestatewiththehighestenergybarrier(0.501eV)is8→9.Allstatesinvolvingthetransferofthe(H++e−)pairwere electrochemicalreactionstates,exceptforthe12→13state(CH *+OCH *→OCH CH *),whichwastheC–Cbondformationandnotinfluencedby 3 2 2 3 appliedpotential.bLocalstructuresoftheactivesiteandintermediatestate.Theballsinbrown,blue,red,grayandwhiterepresentCu,N,O,C,andH atoms,respectively. 8 NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2264,27 +3630,55 @@
           <t>S0200</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Therefore, the peaks, indexed to the absorbed * OCCOH and * OC H on these atop 2 5 C–C coupling on dCu O/Ag could be triggered under catalysts, exhibit a ratio value for * OC H / * OCCOH on dCu O/ asymmetry between * CO 2 and 2 * .</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>C 3% HO (or * COH) following the Ag thatissignificantlygreatercomp 2 ar 5 edwiththatfordCu 2 O 2.3% 2 * CO protonationstep.Notably,adsorbed * CHOintermediate and dCu O/Au .</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>This finding evidences that the key bridge 2 2.3% * was observed on dCu O/Ag from ATR-FTIR spectra, and OC H intermediates for EtOH production are more stable on 2 2.3% 2 5 NATURECOMMUNICATIONS| (2022) 13:3754 |https://doi.org/10.1038/s41467-022-31427-9|www.nature.com/naturecommunications 7</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>P2:CHO intermediate</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2306,19 +3700,47 @@
           <t>S0201</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>This intermediate 4 features *CHO on Sn and *CO(OH) on the neighboring O (i.e., O2Sn-O-CO(OH) bicarbonate), which explains the activities of Sn and O atoms as the dual active centers in the Sn -O3G.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Following the drastic reduction of 1 all carbonyl groups in 4, intermediate 5 is formed as the precursor for C-C coupling.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
+          <t>The free energy barrier to C-C bond formation is 0.13 eV, which is much lower than those of Cu-based catalysts (&gt; 1.0 eV) 13,28.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2340,19 +3762,47 @@
           <t>S0202</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Zhuang, T.-T. et al.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Steering post-C-C coupling selectivity enables high eciency electroreduction of carbon dioxide to multi-carbon alcohols.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Nat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2374,19 +3824,47 @@
           <t>S0203</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>With the increasing current density, the C Faraday effi2 2+ ofproducedethanoltoethylenecanbetunedinthewiderangeafter ciencyremainsatahighlevel,leadingtoanincreasedpartialcurrent hydrophobictreatment(from0.90to1.92)withremarkableFaradaic densityofC products.Thus,aC Faradaicefficiencyofupto80.3% 2+ 2+ efficiencies (FE) of ethanoland C (up to 53.7% and 86.1%, respeccan be maintained even at a high current density of 400mAcm−2, 2+ tively).</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Based on the establishment of this structure, the effect of correspondingtoaC partialcurrentdensityof321mAcm−2,whichis 2+ interfacialwettabilityonthepathwaysofethyleneandethanolisfuramongthebestperformances(Fig.2c,SupplementaryTable2).Further revealed through in-situ spectroscopy and computational fluid thermore, the ethanol-to-ethylene ratio increases from 0.90 to 1.93 dynamicsimulation. andsubsequentlydropsto1.13withtheincreasingofcontactangle from 43° to 131°.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The FE of ethanol is enhanced dramatically, from Results 23.8%to 53.7%,exceeding most reported Cu-based electro-catalysts Characterizationofthewettability-tunablemodifiedCu (Fig. 2d, e, Supplementary Table 2).</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2408,27 +3886,55 @@
           <t>S0204</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>The 6.5h contact with the electrolyte after alkanethiol-modification, which is stabilitytestat−1.2Vversus(vs.)reversiblehydrogenelectrode(RHE) confirmedbytheECSAanalysis.(SupplementaryFig.27,Supplemenshowsthatthestablereductioncurrentdensityandproductselectivity taryTable4).Moreimportantly,formateisthemainproductoftheSaremaintainedafteralkanethiolmodification(SupplementaryFig.17).</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Cu-composedelectrodeinpreviousstudies39–41.However,thecatalyst AccordingtotheSEMimages,XRDprofilesandOH−electroadsorption inthisstudycontributestotheimprovedC product,whichisascri2+ measurement, the morphology and dominant exposed facets of Cu bedtothenewreductionpathwaysofCO RRafterwettabilitymod2 catalyst are not significantly changed (Supplementary Figs. 18–20). ification.Thus,thechemicalstructureormorphologychangingafter XPSanalysisbeforeandaftertheelectrolysisrevealsimilarCu/Sratios thiol-modified is not the reason for improved CO RR selectivity of 2 onthecatalystsurface(SupplementaryFig.21).TheHRTEMdisplays ethyleneandethanol. the presence of the alkanethiol layer on the Cu catalyst after the reactionduetothehighelectrochemicalstabilityofthehydrophobic Effectofcontrollablewettabilityon*COcoverageviaCO mass 2 layer(SupplementaryFig.22).Thehydrophobic-treatedelectrodecan transport maintainalargercontactangleafterelectrolysis,whichascribestothe ItisknownthatthemasstransportofCO (localCO concentration) 2 2 optimized wettabilityofthecatalystlayerthatimprovestheCO RR can affect the coverage of *CO (a precursor of *CO), *CO, and *H, 2 2 stability (Supplementary Fig. 23).</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>In this regard, the exposed facet, which affects the reaction pathways toward ethylene and ethanol morphologyandhydrophobicityoftheCucatalystandthethiollayer further5,20,42.Ourdata(Fig.2)alsomayimplythatthekinetic-controlled after electrolysisare relatively stableunder experimental condition, *CO/*H ratio can be controlled by tuning the local CO /H O ratio 2 2 whichisinaccordancewiththepreviousreport27,34.Additionally,the throughchangingthewettabilityofthecatalyst.Tocircumventthis electrochemicallyactivesurfacearea(ECSA)alsodropsrapidlyafter issue,computationalfluiddynamic(CFD)simulationswereemployed hydrophobic treatment (Supplementary Fig. 24), although the toinvestigatethemasstransportofCO andH Ointhecatalystlayers 2 2 Brunauer–Emmett–Teller specific surface area (S ) is almost relatedtokinetic-controlled*COand*H.Themodelswithandwithout BET unchanged(SupplementaryFig.26),consistentwithpreviousresult27. the alkanethiol modification layer were established to quantity CO 2 Therefore,thelowerECSAandcurrentdensitywiththeformationof alongthecatalystsurface(Fig.3a).Thedifferenceingasdiffusionwas thealkanethiollayercanbeattributedtothereducedcontactwiththe verifiedbysimulatingCO concentration.Theavailabilityofthegas 2 aqueouselectrolyte(Fig.2f,SupplementaryFig.24,25).Thevariation reactant significantly varied at the gas–electrolyte interface after of charge resistance (R ), mass transport resistance (W), and intermodification.Comparingwiththeunmodified-hydrophilicCucatalyst, ct facial electrochemical double-layer capacitance (C) after alkanethiol thegasdiffusiondistanceofthealkanethiol-modifiedlayerisincreased modification in electrochemical impedance spectroscopy (EIS) duetotheimprovedgasdiffusion. 156° 160 131° 112° 120 95° 80 40 0 Cu-4CCu-7CCu-12CCu-18C )°( elgna tcatnoC S 2p Cu-12C 43° Cu 175 170 165 160 Cu ).u.a( ytisnetnI Cu 2p Cu+/Cu0 Cu+/Cu0 Cu-12C Cu2+ Cu 970 960 950 940 930 Binding energy (eV) ).u.a( ytisnetnI Cu(200) Cu(220) Cu 30 40 50 60 70 80 Cu2+ Binding energy (eV) ).u.a( ytisnetnI Article https://doi.org/10.1038/s41467-023-39351-2 a b c Cu(111) Electrolyte Modified layer Alkanethiol Cu Product Product S CO 2 Cu-12C 10 nm Cu 2θ (°) d e f Fig.1|Characterizationofthewettability-tunablemodifiedCuelectrode.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2450,27 +3956,55 @@
           <t>S0205</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Surface atoms in this system were characterized by a pear with increasing CO surface coverage from −0.56 V to −0.76 V , Cu–Cu coordination number of 8.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>To obtain the DFT vibrational freRHE RHE and two new peaks evolve at 1,450 cm−1 and 1,550 cm−1 (Fig. 2c), quencies of CORR reaction intermediates, we first optimized them on 2 which were previously attributed to the *OCCO intermediate15. different active sites on the OD-Cu distorted surface and the crystalline Nature Energy | Volume 9 | December 2024 | 1485–1496 1487 ).u.a( ytisnetnI ).u.a( ytisnetnI a b 8 Cu–CO 7 1,000 cps stretching Cu–CO 6 rotation CO stretching 5 4 P1 P2 3 –1.12 V 2 1 CH stretching 0 –1.04 V –1.2 –1.0 –0.8 –0.6 c 1,182 –0.95 V 1,3181,4531,595 P2 –0.85 V P1 –1.12 V –1.04 V –0.76 V –0.95 V –0.85 V Carbonate –0.56 V 1,550 –0.76 V CuO 2 –0.36 V –0.56 V 1,390 OCP 1,610 –0.36 V 1,000 1,200 1,400 1,600 Raman shift (cm–1) Raman shift (cm–1) 1P/2P fo oitar ytisnetnI 200 300 400 Potential (V) Fig. 2 | In situ SERS measurement during CORR. a, Raman spectra of an CO, ~280 cm−1). c, Zoom-in Raman spectra in the region of 900–1,700 cm−1 from 2 electrochemically treated Cu foil acquired during CORR for potentials ranging about −0.4 V to −1.1 V , with relevant peaks highlighted via dashed lines. 2 RHE RHE from the open-circuit potential (OCP) to about −1.1 V in a CO-saturated 0.1 M The error bars in b correspond to the s.d. of three independent measurements.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>RHE 2 NaClO electrolyte. cps, counts per second. b, Potential-dependent intensity Data are given as average ± s.d. 4 ratio of P2 (Cu–CO stretching, ~360 cm−1) to P1 (restricted rotation of adsorbed</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2492,19 +4026,47 @@
           <t>S0206</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Simulated vibrational frequencies can be visualized through observed in the D-labelling experiment, while the low intensity in the the ioChem-BD database37 (see the explanatory tutorial in Methods 13C/12C exchange experiment did not allow for a robust determination and Supplementary Fig. 17). of the isotope-induced shift.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>In Fig. 3, we show the main reaction intermediates responsible for Since similar C–C coupling intermediates were proposed for the vibrational frequencies detected experimentally (Fig. 2a).</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>After CORR3,38, to validate our observations, we performed in situ SERS the reduction of the Cu oxidic phases, *CO2− and *HCOO−/*HCOOH during CORR.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2526,19 +4088,47 @@
           <t>S0207</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>After CORR3,38, to validate our observations, we performed in situ SERS the reduction of the Cu oxidic phases, *CO2− and *HCOO−/*HCOOH during CORR.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Our data show similar bands (Supplementary Fig. 18). 3 species form (see 1,070 cm−1, 1,390 cm−1 and 1,610 cm−1 signals in Fig. 3; We further prove the appearance of C–C coupling intermediates by Supplementary Tables 1–3).</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
+          <t>Consistent with previous reports14,15, the observing analogous signals on a different Cu foil with distinct surface signals appearing at 1,450 cm−1 and 1,550 cm−1 from −0.76 V can be morphology, yet with still good performance towards C products RHE 2+ attributed to *OCCO(H), with the C=O vibration mode (Fig. 3 and Sup- (Supplementary Fig. 19). plementary Tables 4 and 5).</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2560,19 +4150,47 @@
           <t>S0208</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Besides, the ratio of Faradaic efficiencies towards nelling microscopy41.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Moreover, the subsurface incorporation of 2 ethanol and ethylene continuously increases with increasingly negative atomic impurities such as C or O during CORR cannot be ruled out, as 2 applied potential (Fig. 5a). this could also lead to a defective Cu surface with the modified Raman To further correlate the catalyst structure, surface intermediates shifts obtained here.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Cyclic voltammetry has been used to compare the and reaction products, we carried out quasi in situ Cu LMM XAES, defect density on the Cu surface after CORR using the charge trans2 in situ SERS, cyclic voltammetry and simulations.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2594,19 +4212,47 @@
           <t>S0209</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>20</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>N This effectively prevents the protons in the electrolyte from attacking the O atoms, thereby I E inhibiting dehydration and the loss of oxygen atom, which facilitates the production of EtOH in L C subsequent reactions.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Theoretical calculations of the FTIR spectra of *CHCHO* intermediates I T adsorbed on the surface oRf Co 0.050 -Sub-CuS confirmed the protonation of *CHCO to *CHCHO* A (Fig. 3f and Supplementary Fig. 62).</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>The calculated spectrum showed the C-H stretching in different directions at 1194 cm-1, 1399 cm-1 and 2497 cm-1, which corresponded to the measured results at 1206 cm-1, 1409 cm-1 and 2979 cm-1, respectively (see details in Supplementary Note 2).</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2628,27 +4274,51 @@
           <t>S0210</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>22</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS catalyst, the Cu-Cu distance increases from 2.67 Å to 3.52 Å after the coupling reaction, yielding OCCOH* (Supplementary Fig. 70).</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>In contrast, on Co-Sub-CuS, this distance changes from 2.53 Å to 3.16 Å under the same conditions (Fig. 4b).</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2670,19 +4340,47 @@
           <t>S0211</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="n">
+        <v>35</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>W.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Ma et al., Electrocatalytic reduction of CO to ethylene and ethanol through hydrogen2 assisted C–C coupling over fluorine-modified copper.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Nat.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2704,27 +4402,55 @@
           <t>S0212</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="n">
+        <v>6</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Specifically, the intrinsically generated V and the specific electronic propertiSes of Co-Sub-CuS were proven S S to regulate optimally-distanced dual sites and create asymEmetric active sites, thereby triggering R asymmetric OC-COH coupling due to the blended adPsorption configuration.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>The electron transfer N from Cu to Co, induced by subsurface Co doping, enhances oxophilicity at surface metal sites, I promoting the formation and conversion E of *CHCHO* intermediates via surface-O bonds while L C suppressing the production of *CH*COH intermediates.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DFT predictions combined with in-situ I T isotopic spectroscopy valRidate these findings, capturing the selective determining intermediates A *CHCHO*.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>P3:*COH; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2746,19 +4472,47 @@
           <t>S0213</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>The electrocatalyst after reconstruction, denoted as CA Cu, favored microenvironments to determine the selectivity of CO RR, containedabundantmetallicCuthatservedasactivesitesaswellasa 2 which are inaccessible for conventional external outside to aboveuniqueHelmholtzplaneenrichedwithCA,demonstratingaFaradaic surfacediffusionapproach(Fig.1b).Thisinsidetoon-surfacediffusion efficiency(FE)andapartialcurrentdensity(j)towardC HOHof55.3% 2 5 processcanbeideallyrealizedbyin-situreleasingtheanionsfromthe and 297mAcm−2.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>In-situ spectroscopy techniques verified the interuniquechelatecatalysttothesub-nanoHelmholtzplane.Specially,the molecular interactions between the CA and H O and their positive 2 chelate needs to be characterized by rapid reconfiguration and influenceforenhancedC–CcouplingandsynthesisofC chemicals. 2+ hydrophilic-to-hydrophobicinterfacialwettabilityreversaltoachieve TheoreticalcalculationsrevealedthattheCAmoleculeadsorbedon anionsenrichmentattheHelmholtzplaneandpromoteCO RRprotheCucatalystsurfaceweakenedtheCu–Obondaswellasstabilized 2 cess,beingamajorchallenge.Oncethehydrophilicchelateundergoes the C–O bond in the *OC H intermediate, thus turning the bond 2 3 rapidreconstruction/phasetransformation,thein-situreleasedanions cleavageorderandretainingtheOatomintheintermediate,which will be fast enriched at the Helmholtz plane, where the optimized facilitated the electrosynthesis of C HOH, an oxygen-containing 2 5 interfacial structure and reconfigured hydrophobic catalyst will be chemical, correspondingly inhibited the production of C H ,a non2 4 conducive to the favorable CO RR dynamics as well as restricted oxygen-containing hydrocarbon chemical.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Notably, a self-healing 2 hydrogenevolutionreaction(HER)dynamics.Thisinnovativestrategy processwasachieved by employing the asymmetric pulsed electrowillsimultaneouslyyetwhollyoptimizethereactionprocessinterms lysis,wherethelocalmicroenvironmentthatvariedwiththereaction ofbothcatalystengineeringandinterfaceengineering. process was rebuilt and rejuvenated, creating a consecutively CAHerein,aCuchelateelectrocatalystwasdevelopedtorealizethe enrichedreactionconditioninHelmholtzplanethatenableda conuniqueinsidetoon-surfacediffusionbeyondthetraditionaloutsideto tinuous C HOH electrosynthesis.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2780,19 +4534,47 @@
           <t>S0214</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Consequently, an anions in the Helmholtz plane indeed and manipulate the interface ordered/stable H-bond network derived from the strong intermicroenvironment.Todeeplyintensifythisprocessandalleviatethe molecularinteractionofCAwithH Omoleculesgovernedarestricted gradualdiffusionofCAintothebulkelectrolyteduetoelectrostatic 2 H O adsorptionand activation processes, further inhibited the HER repulsionduringlong-termoperation,weinnovativelyemployedan 2 kinetics. asymmetricpulsedelectrolysismethodtorebuildandrejuvenatethe DFT calculations were carried out to further understand the local chemical microenvironment, sufficiently enriching and concontributionofCAintheCO RRprocess,especiallytheeffectsofC–C tinuouslymaintainingtheCAintheHelmholtzplane.Atthesametime, 2 coupling and hydrocarbon or oxygenated multi-carbon chemicals in order to avoidthe overhigh positive potential during pulse elecselectivity.Thermodynamically,Cu(100)facetwasconducivetoC–C trolysisaffectingthestructureandmorphologyoftheCucatalyst,a coupling,whichwasverifiedbypreviouswork49,50.Consequently,we specific asymmetric pulse electrolysis procedure was designed, i.e., constructedaCu(100)catalystmodelwithandwithoutaCAmolecule −1.6V for 15min, then rapidly switching to 0.1V for 5min (Fig. 6a, adsorbedonthesurface(denotedasCu(100)-CAandCu(100),SupSupplementaryFig.24).Thiscontinuousdynamicpotentialswitching plementary Data1).</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>*CO was a key intermediate in the synthesis of strategy significantly improved the stability of the reaction system, multi-carbonchemicals,andC–CcouplingstepfollowingthereducallowingthecontinuousandstableelectrosynthesisofC HOHforup 2 5 tionofCO toCOwasusuallyregardedastherate-determiningstep51,52. to 40h.</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>As a sharp comparison, the FE was significantly 2 C2H5OH Therefore,theGibbsfreeenergy(ΔG)oftheC–Ccouplingstepcordecreased to less than 40% after 5h reaction in a constant static respondingtoformthekeyOC**COintermediatewascalculated,where electrolysis(Fig.6b).Bycarryingouttheasymmetricpulseelectrolysis, thevalueof ΔGonCu(100)-CAwas0.51eV,significantlylowerthan thedecayrateofFE decreaseddramatically(Fig.6c).Also,the C2H5OH that on the Cu(100) (1.75eV) (Fig. 5d).</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2814,19 +4596,47 @@
           <t>S0215</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>7</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>These drastic changes might originate from the RHE We furthermore followed the reduction of the CuO way that CO predominantly binds to Cu.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>While on pure 2 speciesandtheCOorCO-likeintermediateschemisorbedon CuONCstheCObindingconfigurationissimilarlyproneto 2 Cu and Ag at different potentials and during CORR via Cu@COrotationandstretching,thepresenceofAgsitesgives 2 operando surface-enhanced Raman spectroscopy (SERS). risetoaCObindingconfigurationthatfacilitatestheCu@CO Figure7 presents potential-dependent SERS spectra of the stretchingwiththusstrongerlateralconfinement.WeanticiAgNP-decorated and pure CuONCs acquired at open patethatthelatterplaysacriticalcatalyticroleinenhancing 2 circuitpotential(ocp)andbetween@0.4and@1.1V from the C@C coupling of neighboring CO adsorbates and thus RHE 150–700cm@1and1850–2350cm@1(seealsoFigureS17). increasestheC liquidproductformation. 2+ 7432 www.angewandte.org T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH Angew.Chem.Int.Ed.2021,60,7426–7435 15213773, 2021, 13, Downloaded from https://onlinelibrary.wiley.com/doi/10.1002/anie.202017070 by CochraneAustria, Wiley Online Library on [23/05/2026].</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>See the Terms and Conditions (https://onlinelibrary.wiley.com/terms-and-conditions) on Wiley Online Library for rules of use; OA articles are governed by the applicable Creative Commons License</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2848,19 +4658,47 @@
           <t>S0216</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CO RRproceedsviatheformationofthe*COintermediate,and 2 its subsequent dimerization in CO=CO or *CO–COH intermediates57–59.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>To gain insight into the C–C coupling CO 2 RR using a membrane electrode-assembly (MEA) flow mechanismonfunctionalizedandpristineAg–CuduringCO RR, electrolyzer.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
+          <t>To evaluate the potential of our approach for 2 the surface of the catalysts was probed using operando Raman practical applications towards the electrosynthesis of C 2+ prospectroscopy in order to elucidate the interactions between the ducts, we integrated the different functionalized bimetallic 6 NATURECOMMUNICATIONS| (2021) 12:7210 |https://doi.org/10.1038/s41467-021-27456-5|www.nature.com/naturecommunications</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2882,27 +4720,55 @@
           <t>S0217</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Here, (322) and (221) facet, 5(111)×(100) and 5 The shorter bond length and larger value of –ICOHP indicates (111)×(111), represent s-sq sites and other step sites, thattheC–Obondishardertobreak,whichmeanstheethylene respectively. pathway is inhibited while alcohols pathway is favored.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Indeed, Our calculation shows that CO dimerization reaction over the difference between the Gibbs-free reaction energy to break these four square-like structures are less endothermic than that C–Obondandfurtherprotonationisnegativelycorrelatedtothe over (111) and (221) facet (Fig. 2e, f) under proper electroC–O bond length (Fig. 3d).</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Remarkably, s-sq class, the Cu(211), chemicalinterface.Amongthem,p-sqexhibitsthelowestreaction Cu(533), Cu(755) and Cu(433) [n=3, 4, 6, 7 in n(111)×(100)] energy of −0.16eV.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2924,19 +4790,47 @@
           <t>S0218</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>The electrochemical experiments along with our physicochemical characterizations indicate that the Im improves CO diffusion and balances water content resulting in a higher CO -to-water 2 2 ratio at the catalyst layer and fine-tunes the electronic properties of Mo atoms at the MoP surface.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>In-situ Raman spectroscopy reveals that a high number of adsorbed *CO intermediates on the surface and a higher binding strength of *CO intermediates on the Mo surface sites in the presence of imidazolium molecules are the main reasons for a superior C-C coupling and thereby the improved C H OH formation. 2 5 1 © 2022 published by Elsevier.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
+          <t>This manuscript is made available under the Elsevier user license https://www.elsevier.com/open-access/userlicense/1.0/</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2958,19 +4852,43 @@
           <t>S0219</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="n">
+        <v>21</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
         <is>
           <t>coupling.[43,44] This is consistent with previous studies where it has been confirmed that the intensity ratio of P1 and P2 peaks are potential dependent and higher P2/P1 Raman peak ratios are linked to a higher C-C coupling and C products formation.[43] Furthermore, our in-situ 2+ Raman spectroscopy results show a higher intensity P3 (*C-O stretching) peak of MoP-Im compared to MoP catalyst at the potential of -0.5 V indicating a high concentration/coverage of adsorbed *CO intermediates on the surface of MoP-Im.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
+          <t>These results reveal that the high number of adsorbed *CO intermediateson the surface and the higher binding strength of *CO intermediates on the Mo atoms in presence of the Im are the main reasons for a greater C-C coupling and thereby a higher C H OH production for MoP-Im compared to MoP catalyst. [44] 2 5 4.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2992,19 +4910,47 @@
           <t>S0220</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>21</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Physicochemical 2 characterizations, such as XPS, XANES, and TEM experiments and electrochemical analyses, such as Tafel plot and EIS studies, suggested that the Im works together with MoP nanoparticles to produce C H OH by increasing CO -to-water ratio at the catalyst layer due to 2 5 2 high CO diffusion and hydrophobic properties of the ionomer and alters the electronic 2 properties of the Mo atoms at the surface of the catalyst.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>In-situ Raman spectroscopy confirmed that the imidazolium layer not only increases the number of CO molecules near the catalyst 2 surface but also stabilizes adsorbed *CO – and *CO intermediates at the surface of catalyst that 2 promotes C-C coupling and C H OH formation activity of MoP-Im.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Moreover, DFT calculations 2 5 suggest that the Im can increase the CO binding strength and charge transfer to accelerate the 2 reaction.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3026,19 +4972,47 @@
           <t>S0221</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="n">
+        <v>26</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Cheng, Y.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Wang, Electrocatalytic reduction of CO2 to ethylene and ethanol through hydrogen-assisted C–C coupling over fluorine-modified copper, Nature Catalysis. 3 (2020) 478–487. https://doi.org/10.1038/s41929-020-0450-0. [32] T.-T.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Zhuang, Z.-Q.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3060,19 +5034,47 @@
           <t>S0222</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="n">
+        <v>26</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Yu, E.H.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Sargent, Steering post-C–C coupling selectivity enables high efficiency electroreduction of carbon dioxide to multi-carbon alcohols, Nature Catalysis. 1 (2018) 421–428. https://doi.org/10.1038/s41929-018-0084-7. [33] D.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
+          <t>Karapinar, N.T.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3094,19 +5096,47 @@
           <t>S0223</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>The partially alloyed Cu and Ag phases were confirmed by operando X-ray diffraction.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>By means of combining operando X-ray measurements and density functional theory (DFT) calculations, the preferred carbonyl production is attributed to the reduced electron density and compressive strain of Cu due to Ag incorporation, which leads to a deeper d-band center and therefore weakened intermediate adsorption and oxophilicity.</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
+          <t>This work provides evidence of the intrinsic structural and electronic interaction between Cu and Ag during eCO2RR.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3128,19 +5158,43 @@
           <t>S0224</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="n">
+        <v>32</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>M.; Grätzel, M.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Sequential Catalysis Enables Enhanced C-C Coupling towards Multi-Carbon Alkenes and Alcohols in Carbon Dioxide 32</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3162,19 +5216,47 @@
           <t>S0225</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>The major charge transfer occurred at than the Cu –CuN model (+0.15eV).</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>The CO adsorption 2 3 2 Cu–N site.TheN-dopingplayedanimportantroletoadjustthe energyforCu –CuN andCu –CuN hasbeencalculatedandthe 3 2 3 3 3 electron transfer and further charge distribution between the Cu result shown that the adsorption energy of CO for Cu –CuN 2 2 3 atoms and N-doped carbon interface. and Cu –CuN are +0.24eV and +0.18eV, respectively, 3 3 Theoretical investigations were conducted based on DFT implyingtheadsorptioncapacitiesforCu –CuN andCu –CuN 2 3 3 3 calculations to further understand the reaction mechanism of are close.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
+          <t>However, the corresponding adsorption energy is the Cu–N with triangle pyramid geometry, Cu–CuN , +0.15eV (Cu –CuN ) and −0.36eV (Cu –CuN ), respectively, 3 3 2 3 3 3 Cu –CuN , and Cu –CuN in Supplementary Fig. 20c, f, g, h. indicatingtheadsorptioncapacitiesofHforCu –CuN aremuch 2 3 3 3 3 3 The supported CuN , Cu–CuN , Cu –CuN and Cu –CuN stronger than that for Cu –CuN .</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3196,19 +5278,47 @@
           <t>S0226</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>The *OCHO mechanwiththecompetingreactionofH andCH increasingwhenthe 2 4 ism was preferred for our catalysts than the *CO mechanisms, potential decreased.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>* due to the production of CO was suppressed along with the CH 3 was the key intermediate for C 2+formation rates and it formation ofethanol atthepotentials below−0.8Vas shownin occurred when the potential decreased to −0.6V vs.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
+          <t>RHE.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3230,19 +5340,43 @@
           <t>S0227</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29035-8 Density functional theory calculations.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
+          <t>Theoretical investigabondformationtoCH CH OH.Similarreactionprocessesbased 3 2 tions were conducted based on DFT calculations to further on *OCHO mechanism were considered for Cu –CuN , as well 3 3 understand the reaction mechanism of the Cu –CuN cluster asCuN andCu–CuN whichcontainedonlyoneactiveCusite, 2 3 3 3 withCH * adsorbed.AsupportedCu –CuN clustermodelwith as shownin Supplementary Fig. 29.Thecalculated overpotential 3 2 3 aCubondingwiththreeNatomsonN-dopedcarbonnanosheets (−0.501V) for Cu –CuN cluster was much lower than that of 2 3 was proposed to be the structure of active sites with an applied CuN (−1.685V), Cu–CuN (−1.368V) and Cu –CuN 3 3 3 3 potential of −1.1V vs.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3264,19 +5398,47 @@
           <t>S0228</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>These results shown the 3 3 2 3 3 3 2 3 models with a Cu bonding with three N atoms on N-doped adsorption processes of both CO and H at the Cu –CuN are 2 2 3 carbon nanosheets which were proposed to be the structure of non-spontaneous processes.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>On the contrary, for Cu –CuN , the 3 3 active sites with the applied potential and represents the growth adsorptionoftheHisspontaneousprocess,whiletheadsorption of Cu clusters that may be the active site for the formation of of CO is still non-spontaneous process, illustrating the H 2 ethanol according the results of operando XAS analysis.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The adsorption is advantage state for the competing reaction. reaction pathway of CO RR to CH CH OH for the Cu –CuN Therefore, the larger amounts of H were adsorbed on the 2 3 2 2 3 cluster was investigated combined by the computational hydroCu –CuN sites, which preempted the adsorption sites of CO 3 3 2 gen electrode approach as shown in Fig. 5a, b, Supplementary and reduced the amount of ethanol produced.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3298,19 +5460,47 @@
           <t>S0229</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="n">
+        <v>9</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Operando XAS and XPS results revealed a potentialdataweremeasuredwithfluorescencemodeusingtheAr-filledLytledetector. dependent structure transformation from CuO cluster to Cu –CuN moiety,whichisareversibleprocess.OnceCu –CuN n 3 2 3 clusters have been formed at −1.1V, CO conversion to ethanol OperandoSR-FTIRMeasurements.OperandoSR-FTIRmeasurementswere 2 occurswiththemaximumFE,indicatingtheCu -CuN clusteris conductedattheinfraredspectroscopyandmicrospectroscopystation(BL01B)of 2 3 NationalSynchrotronRadiationLaboratory(NSRL)58.TheCHI660Eelectrothe optimal site.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>The N-doping played an important role to dischemicalworkstation(ShanghaiChenhua,China)wasusedtoapplyvoltagetoa perse the reduced Cu n cluster uniformly and adjust charge disself-madeinfraredreflectioncell.Theinfraredspectrumswerecollectedusing tributionbetweenmetalatomsandsubstrate.OperandoFTIRand BrukerVertex70V/sFTIRspectrometerwithnitrogencooledmercurycadmium theoretic calculations results demonstrated that CH * was the telluridedetector,andthesynchrotronradiationinfraredbeamwasfocusedonthe major intermediates and Cu –CuN clusters wer 3 e chargereflectioncellusingBrukerHyperion3000microscopeequippedwitha×15 2 3 objective.Inthemeasurements,thegapbetweentheworkingelectrodeandthe asymmetric sites that are intensified by CH 3 * adsorbing.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The ZnSewindowwascarefullymaintainedontheorderofmicronstoprevent charge-asymmetric sites are responsible for the outstanding excessivewaterabsorption.Allspectrumswerecollectedusingsingle-potential asymmetry ethanol formation.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3332,19 +5522,43 @@
           <t>S0230</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
         <is>
           <t>ARTICLE OPEN https://doi.org/10.1038/s41467-022-31427-9 – – Boosting electrocatalytic CO to ethanol 2 – production via asymmetric C C coupling Pengtang Wang1,2,4, Hao Yang 3,4, Cheng Tang1, Yu Wu3, Yao Zheng 1, Tao Cheng 3, Kenneth Davey 1, ✉ ✉ Xiaoqing Huang 2 &amp; Shi-Zhang Qiao 1 Electroreduction of carbon dioxide (CO ) into multicarbon products provides possibility of 2 large-scale chemicals production and is therefore of significant research and commercial interest.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, the production efficiency for ethanol (EtOH), a significant chemical feedstock, is impractically low because of limited selectivity, especially under high current operation.Herewereportanewsilver–modifiedcopper–oxidecatalyst(dCu O/Ag )that 2 2.3% exhibitsasignificantFaradaicefficiencyof40.8%andenergyefficiencyof22.3%forboosted EtOH production.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3366,27 +5580,55 @@
           <t>S0231</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="n">
+        <v>7</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>With PCET, the carbonyl group in HCOOH* can easily dehydrate to 2 generate Sn-CHO in intermediate 4, with a free energy barrier of 0.52 eV.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>This intermediate 4 features *CHO on Sn and *CO(OH) on the neighboring O (i.e., O2Sn-O-CO(OH) bicarbonate), which explains the activities of Sn and O atoms as the dual active centers in the Sn -O3G.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Following the drastic reduction of 1 all carbonyl groups in 4, intermediate 5 is formed as the precursor for C-C coupling.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3408,19 +5650,43 @@
           <t>S0232</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-023-39351-2 Tunable CO electroreduction to ethanol and 2 ethylene with controllable interfacial wettability Received:21November2022 YanLin1,2,3,5,TuoWang 1,2,3,4,5,LiliZhang1,2,3,GongZhang 1,2,3,LuluLi1,2,3, QingfengChang1,2,3,ZifanPang1,2,3,HuiGao1,2,3,KaiHuang1,2,4, Accepted:8June2023 PengZhang 1,2,3,4,Zhi-JianZhao 1,2,3,ChunleiPei1,2,3&amp;JinlongGong 1,2,3 Checkforupdates ThemechanismofhowinterfacialwettabilityimpactstheCO electroreduc2 tionpathwaystoethyleneandethanolremainsunclear.Thispaperdescribes thedesignandrealizationofcontrollableequilibriumofkinetic-controlled*CO and*Hviamodifyingalkanethiolswithdifferentalkylchainlengthstorevealits contributiontoethyleneandethanolpathways.CharacterizationandsimulationrevealthatthemasstransportofCO andH Oisrelatedwithinterfacial 2 2 wettability,whichmayresultinthevariationofkinetic-controlled*COand*H ratio,whichaffectsethyleneandethanolpathways.Throughmodulatingthe hydrophilicinterfacetosuperhydrophobicinterface,thereactionlimitation shiftsfrominsufficientsupplyofkinetic-controlled*COtothatof*H.The ethanoltoethyleneratiocanbecontinuouslytailoredinawiderangefrom0.9 to1.92,withremarkableFaradaicefficienciestowardethanolandmulti-carbon (C )productsupto53.7%and86.1%,respectively.AC Faradaicefficiencyof 2+ 2+ 80.3%canbeachievedwithahighC partialcurrentdensityof321mAcm−2, 2+ whichisamongthehighestselectivityatsuchcurrentdensities.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The electrochemical conversion of carbon dioxide (CO ) into Astheonlymetalwithanegativeadsorptionenergyfor*CObuta 2 value-addedmulti-carbon(C )productsisanattractiverouteto positive adsorption energy for *H, copper (Cu) presents a unique 2+ closethecarbonloop1,2.However,theformationofC products abilitytoproduceC products4,9.However,multipleproductshave 2+ 2+ with high selectivity is still meeting great challenges3.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3442,19 +5708,47 @@
           <t>S0233</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="n">
+        <v>9</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Note that the solvent effect for ionconvectionismainlydeterminedbytheelectrostaticforcesand OCCO*wassimulatedusingpolarisedexplicitwatermodels,forwhich notbythefluidinertia34,43.Theionconcentrationsnearsurfacesare the uncertainty of the adsorption energy has been reported to be mainlygovernedbytheappliedvoltages.Afterafewmicroseconds, negligible20. the concentrations of ions in the 30nm pores reach a quasi-steady state,anorderofmagnitudehigherthanthatontheflatsurfaceorin Energyglobaloptimization the150nmpores.Thenumericalsimulationsshowedthat30nmpores By considering the elementary steps in the simplified reaction netincreasedthepotassiumconcentrationsnearthesurfaces.Asaresult, work, all possible pathways can be enumerated24,25.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>The elementary hydrogenevolutionreaction(HER)issuppressed. stepwiththehighestlimitingenergywasdefinedasthelimitingstepin aspecificpathway(r ,r ,andr inSupplementaryFig.3).Thepathway Dataavailability A B C with the lowest limiting energy among all possible pathways was Sourcedatatogeneratefiguresandtablesareavailablefromthecorchosen as the most favoured pathway (red path in Supplementary respondingauthors.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
+          <t>Fig.3),withtherelevantlimitingenergydefinedastheG -limiting RPD energy(G ),asfollows: References RPD h (cid:4) (cid:5)i 1.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3476,19 +5770,47 @@
           <t>S0234</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>C.; Surendranath, Y.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Ethylene and Ethanol through Hydrogen-Assisted C−C Coupling Donor-DependentPromotionofInterfacialProton-CoupledElectron over Fluorine-ModifiedCopper.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Nat.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3510,19 +5832,47 @@
           <t>S0235</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="n">
+        <v>9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ACS Catalysis pubs.acs.org/acscatalysis ResearchArticle synthesis.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>The ethanol formation rate shows a minimum CO adsorption and thus the coupling between acetaldehyde between 12.5 and 17.5 mL min−1 of CO flow while the and CO is compromised. propanol formation rate increases significantly, reaching its ■ maximum at 17.5 mL min−1.</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The fact that the production of ASSOCIATED CONTENT ethanolisminimalwhentheproductionofn-propanolreaches * sı Supporting Information its maximum suggests that methylcarbonyl is an intermediate The Supporting Information is available free of charge at fortheformationofbothmolecules.Thistrendisnotobserved https://pubs.acs.org/doi/10.1021/acscatal.3c00190. for ethylene formation (Figure 5a), indicating that methylSEM images of the Cu electrode surface, acetaldehyde carbonyl is not an intermediate in the ethylene pathway. conversion in the absence and in the presence of CO, Finally, our results show that low flow rates are not beneficial and Faradaic efficiency for H and carbon products at as a high local CO concentration is needed to form the key 2 different CO partial pressures (PDF) CO−dimer and the corresponding C intermediates, such as 2 methylcarbonyl.21−23 Recently, Hou et al.32 have showed that ■ the increase in CO coverage, by increasing the CO pressure, AUTHOR INFORMATION favorstheselectivitytowardoxygenates,especiallyacetate,over Corresponding Author ethylene.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3544,19 +5894,47 @@
           <t>S0236</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>The ethanol route opens up only in the presence of highly compressed and distorted Cu domains with deep s-band states via the crucial intermediate *OCHCH .</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>By identifying and tracking the 2 critical intermediates and specific active sites, our work provides guidelines to selectively decouple ethylene and ethanol production on rationally designed catalysts.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Electrochemical reduction of CO (CORR) to chemicals is a promising coverage and selectivity towards C products exists13.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3578,27 +5956,55 @@
           <t>S0237</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>In Fig. 3, we show the main reaction intermediates responsible for Since similar C–C coupling intermediates were proposed for the vibrational frequencies detected experimentally (Fig. 2a).</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>After CORR3,38, to validate our observations, we performed in situ SERS the reduction of the Cu oxidic phases, *CO2− and *HCOO−/*HCOOH during CORR.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Our data show similar bands (Supplementary Fig. 18). 3 species form (see 1,070 cm−1, 1,390 cm−1 and 1,610 cm−1 signals in Fig. 3; We further prove the appearance of C–C coupling intermediates by Supplementary Tables 1–3).</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3620,19 +6026,43 @@
           <t>S0238</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Moreover, defective structures and highly disordered Cu(0)/ CO adsorbed on defect Cu sites, further increase and reach a maximum Cu(I,II) interfaces created through pulsed electrolysis conditions were at −1.04 V , coinciding with the detection of the *OCHCH key interfound to significantly enhance ethanol selectivity25,45,46.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Thus, we iniRHE x mediate and ethanol. tially assessed the role of two structural descriptors to identify defects Nature Energy | Volume 9 | December 2024 | 1485–1496 1489 ).u.a( ytisnetnI ).u.a( ytisnetnI 1,602 Raman shift (cm–1) Fig. 4 | In situ SERS measurement and DFT vibrational analysis with vibrational fingerprints on selected active sites determined by DFT simulations the isotope exchange. a, Raman spectra of species adsorbed on the for 12C and 13C (see Methods, ref. 62). c, Raman spectra of an electrochemically electrochemically treated Cu electrode at −0.95 V in 13CO-saturated 0.1 M treated Cu foil acquired in 0.05 M glyoxal for potentials ranging from −0.3 V to RHE 2 RHE NaClO electrolyte and CO-saturated 0.1 M NaClO DO electrolytes. b, OCHCH about −1.0 V in an Ar-saturated 0.1 M NaClO electrolyte. 4 2 4 2 2 RHE 4</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3654,19 +6084,47 @@
           <t>S0239</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41560-024-01633-4 –1.5 7 Crystalline domains 2.5 8 7 7 6 Crystalline domains 7 7 8.03 7 9 5 –1.8 5 5 2.0 9 5 5 6 –2.1 8 6.97 1.5 7 4 7.48 7 6.17 4 1.0 6.49 6.17 4 4 9.42 6 6 .49 6 7.48 0.5 6.97 8.03 9.42 5.00 4.46 5 Distorted domains 4.46 Distorted domains 5.00 0 Proposed reaction scheme for CO RR to C rate-determing step (RDS) towards multi-carbon molecules during 2 2+ products CO reduction.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Such hypothesis has been recently challenged by 2 The proposed OCHCH -mediated ethanol pathway suggests an mechanistic studies of CO reduction50; thus, competing RDSs may 2 updated reaction scheme for CORR towards C products (Fig. 7). exist depending on the catalyst morphology.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>If formed, the CO–CO(H) 2 2+ Ethylene and ethanol formations are pH-independent on the RHE species is characterized by either a single or double C–C bond7 scale5.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3688,19 +6146,47 @@
           <t>S0240</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>*CHCO can then either reduce to at a sweep rate of 10 mV s−1 from −1.3 V to +0.9 V for two cycles.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>RHE RHE *OCCH along the acetate/ethanol pathway or undergo reduction to 2 ethylene via five proton-coupled electron transfers and the release Characterization of samples of one HO molecule21.</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Along the acetate/ethanol route, OCCH can The crystal structure of the catalysts was studied using XRD with a 2 2 desorb and react in solution with OH− to form acetate21.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3722,19 +6208,47 @@
           <t>S0241</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RHE RHE *OCCH along the acetate/ethanol pathway or undergo reduction to 2 ethylene via five proton-coupled electron transfers and the release Characterization of samples of one HO molecule21.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Along the acetate/ethanol route, OCCH can The crystal structure of the catalysts was studied using XRD with a 2 2 desorb and react in solution with OH− to form acetate21.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Following the Bruker-AXS D8 Advance in parallel beam configuration equipped with C route, when highly strained distorted sites are present, an alternative a Cu X-ray tube, a Goebel mirror and equatorial Soller slit (0.3°) as well 2 reaction pathway opens, that is, enabling the reduction of *OCCH to as an energy-dispersive LynxEye detector.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3756,27 +6270,55 @@
           <t>S0242</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-54636-w equipped with a flame ionization detector (FID) for CO, CH and vibrational entropy was considered, which was calculated from the 4 C H , and a thermal conductivity detector(TCD)forH .</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Ultrapure DFTcalculatedvibrationalfrequencies.Theactivationbarrierofeach 2 4 2 nitrogen(N ,99.9999%)wasusedasthecarriergas.Theliquidproreactionwasobtainedfromclimbing-imagenudgedelasticband(CI2 ducts(HCOOHandCH CH OH)wereexaminedbynuclearmagnetic NEB)calculations73. 3 2 resonancespectroscopy(NMR).1HNMRand13CNMRspectrawere collectedonaBrukerAvanceIIIHD400NMRspectroscopein10% Dataavailability D O using water suppression mode, with DMSO as an internal Theex-situXPSdata,ex-situXASdata,productquantification,quasiin2 standard. situ XPS data, operando XAS data, operando Raman data, operando The Faradaic efficiency (FE) was calculated using the following ATR-SEIRASdata,isotopiclabellingexperimentdataandtheoretical equation: calculationsdatageneratedinthisstudyhavebeendepositedinthe Figsharedatabaseunderaccessioncode(https://doi.org/10.6084/m9.</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>FE i= Q Q tot i al = z i× I F × × t N i = I z × i× R v × i T × o G × × 6 F 0 × 00 P o 0 figshare.27199515)74.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3798,19 +6340,47 @@
           <t>S0243</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>For instance, Cu-Ag catalyst often shows peaks,which can be assigned to fcc Cu (SupplementaryFig. 8), indihigh activity for the formation of C hydrocarbons and catingatomicdispersionofAgatomsinAgCuNW45.WhileforAgCu 2+ 1 oxygenates33,34.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>However, the tandem approach usually leads to NW,diffractionpeaksofbothmetallicCuandAgareclearlyobservable. uncontrolledC-Ccoupling,producingavarietyofC productssuchas The contents of Ag in AgCu NW and AgCu NW were measured by 2+ 1 ethylene,ethanol,andacetatethroughcascadecatalysis.Grätzeletal.35 inductivelycoupledplasmaemissionspectrometer(ICP)andtheresults andYangetal.34suggestedthattheefficient*COspilloverfromAgto aresummarizedinSupplementaryTable2.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Cucouldimprovesethyleneperformance.Qiaoetal.23claimedthat Thesurfacevalencestatesofthe as-synthesizedCu NW,AgCu 1 significantly boosted ethanol production could be achieved by the NWandAgCuNWwereanalyzedbyX-rayphotoelectronspectroscopy tailoredintroductionofAgtooptimizethecoordinatednumberand (XPS).ThesurveyXPSspectrashowagradualincreaseoftheAgpeak oxidationstateofsurfaceCusites.However,duetothecomplexityand withincreasingAgcontent(SupplementaryFig.9andSupplementary diversity of the catalyst’s structure, the underlying mechanism of Table3).Thehigh-resolutionO1sXPSspectrumofCuNW,AgCuNW 1 CO RRtoethylene/ethanolintheCu-Agsystemremainsunclear34,36,37. andAgCuNWexhibitsimilarcharacteristicpeaksat530.5and532.4eV, 2 Recently,therapiddevelopmentofsingle-atomcatalysishasopened whicharerelatedtoadsorbedsurfacehydroxide(OH )andadsorbed ads upnewpossibilitiesforconstructingmodelcatalystswithasymmetric water (H O ), respectively (Supplementary Fig. 10)46.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3832,27 +6402,55 @@
           <t>S0244</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>A distinct H O 2 3 2 adsorbed*COwereidentifiedat282,362and1950–2150cm−1,correabsorptionpeakataround1620cm−1wasobservedoverallcatalysts57. sponding to Cu-CO frustrated rotation (denoted as P1), Cu-CO AsshowninFig.4d,twopeaksappearedataround2050and1865cm−1 stretching (denoted as P2) and C-O stretching, respectively54. over AgCu NW, which are associated with the atop-adsorbed *CO Figure4cdisplaysthepotential-dependentintensityratiosbetweenP2 (*CO ) and bridge-adsorbed *CO (*CO ) on Cu surface, atop bridge andP1overAgCuNWandAgCuNW.ComparedtoAgCuNW,the respectively23,58,59.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>The red-shift of the *CO peaks with increase in 1 1 higherP2/P1ratiosobservedoverAgCuNWsuggesthigher*COcovappliedcathodicpotentialisduetotheStarkeffectarisingfromthe erages on the AgCu NW surface, which shall benefit formation of decreasedresonancefrequenciesinnegativeelectricfields38.Inparti- *COCOintermediatesforethyleneproduction35,55.Besides,theRaman cular, the absorption peak of the *COCO intermediate at 1561cm−1 peaksat704,1072and1556cm−1observedacrossthepotentialrange appeared at −0.4V vs.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>RHE and reached the maximum intensity at from−0.6to−1.4Vvs.RHEcanbeassignedtoin-planeνCO -,adsorbed −1.2Vvs.RHE,whichispositivelycorrelatedwiththeethyleneFaradaic 2 carbonatespecies(νCO 2-)andν CO −,respectively53.OverAgCuNW, efficiency, suggesting that*COCO iscrucial for ethylene generation 3 as 2 1 acharacteristicpeakat537cm−1thatcanbeassignedto*OHspecies, overAgCuNW(Fig.4d,f)12.Additionally,aclearabsorptionpeakcould wasobservedat−0.6Vvs.RHE,whichgraduallygrewwithincreasing beidentifiedat1400cm−1thatcanbeassignedtotheadsorbed*COOH NatureCommunications|( 2024)1 5:10247 5</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3874,19 +6472,47 @@
           <t>S0245</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-54636-w Fig.5|Theoreticalinsightsintothecatalyticmechanisms.a,bTheadsorption ethyleneoverAgCuNW.eProposedreactionpathwayforCO reductionto 1 2 anddissociationenergiesofH2OonCuNW,AgCuNWandAg1CuNW.cGibbsfree ethanoloverAg1CuNW.TheinsetinFig.5a,candeshowstheDFT-optimized energydiagramsfor*COhydrogenationto*CHOoverCuNW,Ag1CuNWandHOstructures.(Cu:yellow,Ag:gray,O:red,H:white,C:blackgray).</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>AgCuNW.dCalculatedGibbsfreeenergydiagramsforCORRtoethanoland 1 2 AgCuNWcandonateelectronstoitsneighboringCuatoms,moving to0.63eV,revealingpreferredproductionof*COviathe*COOHroute 1 the d-band center of Cu from −2.142 to −2.132eV.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
+          <t>Meanwhile, the overAgCuNW.Theincreased*COcoverageshallincreasetheprobatomicallydispersedAgatombecomespositivelycharged,matching ability of *CO-*CO coupling to form *COCO intermediate, directing wellwiththeXPSandXASresults.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3908,27 +6534,55 @@
           <t>S0246</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>21</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Subsequently, the shared intermediate *CHCO transformed into *CHCHO* via surface-O bonds by hydrogenated carbon atoms, followed by the next protonation step through the adsorption of O atoms.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>The complete reaction pathway from CO to EtOH on Co -Sub-CuS is as follows: 2CO 2 0.050 2 → 2*COOH → *CO + *CO → *COH + *CO → *OCCOH → *CCO → *CHCO → bridge atop atop *CHCHO* → *OCHCH → *OCHCH → *OCH CH → C HSOH (Fig. 3k).</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>The design of 2 3 2 3 2 5 S subsurface Co-doped CuS selectively directs EtOH produEction by promoting asymmetric C-C R coupling and controlling the branching pathway.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P3:*COH</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3950,19 +6604,47 @@
           <t>S0247</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>21</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS *CO , resulting in asymmetric OC-COH coupling, which is further supported by in-situ Raman bridge spectroscopy (Fig. 3g-i and Supplementary Figs. 64-67, see details in Supplementary Note 3).</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Subsequently, the shared intermediate *CHCO transformed into *CHCHO* via surface-O bonds by hydrogenated carbon atoms, followed by the next protonation step through the adsorption of O atoms.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
+          <t>The complete reaction pathway from CO to EtOH on Co -Sub-CuS is as follows: 2CO 2 0.050 2 → 2*COOH → *CO + *CO → *COH + *CO → *OCCOH → *CCO → *CHCO → bridge atop atop *CHCHO* → *OCHCH → *OCHCH → *OCH CH → C HSOH (Fig. 3k).</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3984,19 +6666,47 @@
           <t>S0248</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>21</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>The complete reaction pathway from CO to EtOH on Co -Sub-CuS is as follows: 2CO 2 0.050 2 → 2*COOH → *CO + *CO → *COH + *CO → *OCCOH → *CCO → *CHCO → bridge atop atop *CHCHO* → *OCHCH → *OCHCH → *OCH CH → C HSOH (Fig. 3k).</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>The design of 2 3 2 3 2 5 S subsurface Co-doped CuS selectively directs EtOH produEction by promoting asymmetric C-C R coupling and controlling the branching pathway.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
+          <t>P N I E DFT Calculations L C To investigate the role of subsurface cobalt in controlling the selectivity of C products, DFT 2 I T calculations were performRed.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4018,19 +6728,47 @@
           <t>S0249</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>21</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>The design of 2 3 2 3 2 5 S subsurface Co-doped CuS selectively directs EtOH produEction by promoting asymmetric C-C R coupling and controlling the branching pathway.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>P N I E DFT Calculations L C To investigate the role of subsurface cobalt in controlling the selectivity of C products, DFT 2 I T calculations were performRed.</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
+          <t>The analysis of CO 2 ER selectivity begins with examining the coA adsorbed state of *CO and *COH, which is a critical initial step in the competing reaction pathways54,55.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4052,19 +6790,47 @@
           <t>S0250</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="n">
+        <v>27</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>S S E R Discussion P N I E In summary, Co subsurface-doped CuS with rich sulfur vacancies on the surface was synthesized L C via a one-pot redox solvothermal method.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Combining in-situ isotopic spectroscopy and DFT I T calculation prediction, it wRas found that subsurface Co doping effectively regulates dual sites at an A optimal distance, creating asymmetric active sites through surface V and surface-subsurface S electron interactions.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
+          <t>The asymmetric coupling of OCCOH was triggered by promoting a mixed adsorption configuration of *CO and *CO .</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4086,19 +6852,47 @@
           <t>S0251</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>35</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>J.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Zhang et al., Steering CO electroreduction pathway toward ethanol via surface-bounded 2 P hydroxyl species-induced noncovalent interaction.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Proc.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4120,19 +6914,47 @@
           <t>S0252</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="n">
+        <v>36</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>K.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Yao et al., Mechanistic Insights into OC-COH Coupling in CO Electroreduction on R 2 Fragmented Copper.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
+          <t>J.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4154,19 +6976,47 @@
           <t>S0253</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>36</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>P.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Wang et al., Boosting electrocatalytic CO -to-ethanol production via asymmetric C-C 2 coupling.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Nat.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4188,19 +7038,47 @@
           <t>S0254</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="n">
+        <v>38</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Wang, P. et al.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Boosting electrocatalytic CO –to–ethanol production via asymmetric C–C 2 coupling.</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Nat.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4222,19 +7100,47 @@
           <t>S0255</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>The electron transfer N from Cu to Co, induced by subsurface Co doping, enhances oxophilicity at surface metal sites, I promoting the formation and conversion E of *CHCHO* intermediates via surface-O bonds while L C suppressing the production of *CH*COH intermediates.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>DFT predictions combined with in-situ I T isotopic spectroscopy valRidate these findings, capturing the selective determining intermediates A *CHCHO*.</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
+          <t>Consequently, in a flow cell, the optimized Co-Sub-CuS catalysts exhibited a Faradaic efficiency (FE) of 87.6% and 79.4% for C and EtOH products at a partial current density of 602.0 2 mA cm−2, with a stability over 410 h.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4256,19 +7162,47 @@
           <t>S0256</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>In this work, we developed a facile and scalable strategy to synthesize subsurface Co-doped CuS catalysts (Co-Sub-CuS) featuring abundant sulfur vacancies (V ) and surface-subsurface S electron interactions, enabling the directional selectivity of CO electroreduction to EtOH through 2 the branching pathway from *CHCO to *CHCHO* following promoted C-C coupling.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Specifically, the intrinsically generated V and the specific electronic propertiSes of Co-Sub-CuS were proven S S to regulate optimally-distanced dual sites and create asymEmetric active sites, thereby triggering R asymmetric OC-COH coupling due to the blended adPsorption configuration.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
+          <t>The electron transfer N from Cu to Co, induced by subsurface Co doping, enhances oxophilicity at surface metal sites, I promoting the formation and conversion E of *CHCHO* intermediates via surface-O bonds while L C suppressing the production of *CH*COH intermediates.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4290,19 +7224,47 @@
           <t>S0257</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>A key point of debate is whether oxygen-containing CO isconductedin0.1MKHCO (SupplementaryFig.3a),and 2 3 species,e.g.,CuO ,CuO (OH) ,andCu(OH) ,arepresentatthe the results are consistent with the previous reports on polyx x y x CO 2 RRconditions6,7,10–19.Multipleexsituandinsitu/operando crystallineCucatalysts29,30.ThemajorC 2+productsareethylene, characterizations lead to contradicting conclusions6,7,10–17,19.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>As ethanol, n-propanol, and acetate, and the major C products are 1 ex situ measurements have the potential of exposing the sample methane, CO, and formate.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The co-electrolysis is performed by to the ambient condition, the origin of the oxygen-containing feedingamixtureofCO andO withmoleratiosof9:1and8:2. 2 2 speciesontheCusurfacedetectedbythesemethodsisuncertain.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4324,19 +7286,43 @@
           <t>S0258</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" t="n">
+        <v>9</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-021-27456-5 firstlyelectrodepositedongasdiffusionlayer(GDL,Sigracet22BB,FuelCellStore) QuantificationoftheCO 2 RRproducts.Theelectrochemicaldatawererecorded usedasgasdiffusionelectrode(GDE)andthenfunctionalsolutionsweredropwhilesimultaneouslycollectingtheCORRgasproductsbyusinganautomatic 2 coatedonthecatalystside,whiletheothersideoftheGDLwascoveredwith samplerconnectedtothecathodeoutlet.Acoldtrapwasusedtocollecttheliquid polyamidetape.TheGDLwasthentapeonagraphitefoilandsubsequently,the productsbeforethesampler.Foreachappliedpotential,thegasproductswere electrodewasmountedinanoperandocellwiththegraphitefoilactingasa collectedatleastthreetimeswithpropertimeintervals.Thegasaliquotswerethen workingelectrodeandwindow.A0.5MsolutionofKHCO wasusedaselectrolyte injectedintoanonlinegaschromatograph(Agilent,MicroGC-490)equippedwith 3 fortheCORRandthecellwascontinuouslypurgedwithCO duringthemeaaTCDdetectorandMolsieve5Acolumncontinuously.Hydrogenandargon 2 2 surements.Allmeasurementswereperformedatconstantpotentialsof−1.2V, (99.9999%)wereusedasthecarriergases.Liquidproductswerequantifiedby1H −1.1V,−1.0Vand−0.9Vvs.RHE.Time-resolvedspectrawererecordedevery NMRspectroscopy(600MhzAvanceIIIBukrerwithacryorobeProdigyTCI) 30minuntilnofurtherchangeswereobservedunderCORRconditions. usingdeionizedwaterwith0.1%(w/w)ofDSS(Sodiumtrimethylsilylpropane2 DataalignmentandnormalizationoftheX-rayabsorptionnear-edgestructure sulfonate)likeinternalstandardforthequantificationoftheethanolandformate.</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
+          <t>(XANES)spectrawereconductedbyusingtheAthenasoftware.TofittheCu An1Dsequencewatersuppressionwithexcitationsculptingwithgradients(zgesgp) K-edgeextendedX-rayabsorptionfinestructure(EXAFS)spectraχ(k)k2,therange wasusedfortheacquisition(Numberofscan=32,DelayD1=30s).Owingtothe ofparameterRinR-spacefromR =1ÅuptoR =2.1Åwasusedforthe liquidproductcrossover,theFEvaluesoftheliquidproductswerecalculatedbased min max freshlypreparedcatalysts,whileR =1.0ÅtoR =3.0Åwereusedforthe onthetotalamountoftheproductscollectedontheanodeandcathodesides reductivecatalysts.Thek-rangefro m m in 3.0Å−1to10 m .0 ax Å−1withak-weightingof1, duringthesameperiod. 2,and3wereappliedintheFouriertransforms.Allfittingparametersincludingthe c C o u o – r C di u na p t a i t o h n s, n a u s m w b e e ll rs as N t , h i e nt c e o r r a r t e o c m tio ic n d s i t s o ta t n h c e es ph R o , t d o i e s l o e r c d tr e o r n fa r c e t f o e r r s en σ2 ce fo e r n C er u g – ie O sΔ an E d 0 M St E ab A ili e t l y ec m tro e l a y s z u er re w m a e s n o t p s e i r n at t e h d e a M ta EA con co st n a fi nt gu v r o a lt t a io ge n. o F f o − r 4 t . h 5 e 5 s V tab w i i l t i h ty c t o e n st t , in th u e ous wereobtained.TheS2factorsweresetto0.831. 0 feedinginCO.Thegasproductswerecollectedatfrequenttimeintervals.TheFE 2 valueswerecalculatedfromtheaveragevalueobtainedfromthreesuccessive Computationaldetails.Alldensityfunctionaltheory(DFT)calculationswere injections.Asfortheliquidproducts,thetotalliquidproductswerecollectedatthe carriedoutintheViennaAb-initioSimulationPackage(VASP)codewiththe endoftheexperiments. projectoraugmented-wave(PAW)method.Theexchange–correlationenergywas t P r e e r a d te e d w– u B si u n r g ke a – g E e r n n e z r e a r l ho gr f a ( d P i B en E t ) a f p o p rm ro a x l i i m sm a . ti A on p ( l G an G e A -w ) a w ve ith ba t s h is e withakinetic Faradaicefficiencyandenergyefficiencycalculations.TheFaradaicefficiency (FE)ofeachgasproductwascalculatedasfollows: energycutoffof500eVwaschosentoexpandtheelectronicwavefunctions.To i a n 5 ve l s a t y ig e a rs te o t f h C e u po ( s 1 s 1 ib 1) le s b la i b nd ( i 7 n .7 g 3 m 86 od Å es × b 7 e . t 7 w 3 e 8 e 6 n Å fu ), n i c n ti w on h a ic l h m t o h l e ec t u w la o r b a o n t d to c m ata la ly y s e t r s s , FE gas ¼g i ´v´ R z T i FP 0 ´ I 1 ´100% ð3Þ werekeptfixedduringrelaxation,wasbuiltwithavacuumspaceofabout20Å.For TheFaradaicefficiency(FE)ofeachliquidpr to o t d al uctwascalculatedasfollows: thegeometricaloptimizations,allatomswerefullyrelaxedtothegroundstatewith t w h h e e c re on a v 3 er × ge 3 n × ce 1 o Γ f -c e e n n e t r e g r y ed an M d o f n o k r h ce o s rs s t e - t P ti a n c g k t s o ch 1 e . m 0× ed 10 k − -m 5e e V sh a w n a d s 0 u . s 0 e 1 d e t V o Å sa − m 1 p , le FE liquid ¼l i ´ Q z to i tal F´100% ð4Þ thefirstBrillouinzone.Tocomparethebondstrengthbetweeneachgroupof Theformationrate(R)foreachspecies(i)wascalculatedasfollows: u fu s n in c g tio th n e al fo m ll o o l w ec i u n l g ar fo a r n m d u C la u : (111),theadsorptionenergy(E ads )iscalculatedby R i ¼ 96; Q 48 to 5 ta ´ l ´ z F ´ E t i ´S ð5Þ i E ads ¼E Cu=FM (cid:2)E Cu (cid:2)E FM ð1Þ Thefull-cellenergyefficiencies(EE)wascalculatedasfollows: whereE Cu/FM ,E Cu ,andE FM denotethetotalelectronicenergiesofanadsorbed EE¼ ð1:23(cid:2)E i Þ´FE i ð6Þ system,acleanCu(111)surface,andthefreefunctionalmolecular,respectively.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4358,19 +7344,47 @@
           <t>S0259</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Tables 4–6).</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Here, (322) and (221) facet, 5(111)×(100) and 5 The shorter bond length and larger value of –ICOHP indicates (111)×(111), represent s-sq sites and other step sites, thattheC–Obondishardertobreak,whichmeanstheethylene respectively. pathway is inhibited while alcohols pathway is favored.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
+          <t>Indeed, Our calculation shows that CO dimerization reaction over the difference between the Gibbs-free reaction energy to break these four square-like structures are less endothermic than that C–Obondandfurtherprotonationisnegativelycorrelatedtothe over (111) and (221) facet (Fig. 2e, f) under proper electroC–O bond length (Fig. 3d).</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4392,19 +7406,47 @@
           <t>S0260</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>120 H Fromate CO CH 2 2 4 Methanol Ethanol n-Propanol 100 80 60 40 20 0 -1.5 -1.4 -1.3 -1.2 -1.1 -1.0 -0.9 electrochemically stable than Hex-2Cu-2O, and hence the CO RR spectraofOct-2Cubeforeandafterelectrolysisdisplayasimilartrend 2 activityoftheformermusthavecomefromitsmutatedstructure.For to that of Hex-2Cu-O, indicating thatCu2+ inthe moleculewas also Oct-2Cu,post-electrolyticMSdidnotdetectanysignalsfromtheorireduced to Cu+/Cu0 (Supplementary Fig. 18).</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>No Cu2+ state was ginalmacrocycles(i.e.Oct-2CuorOctaphyrin)otherthanabunchof observed in the Cu 2p spectrum of Oct-2Cu after electrocatalysis fragmentsbelowm/z=1100(SupplementaryFig.12).Thisindicatesthe (SupplementaryFig.19).FurtherintheAugerCuLMMspectra,postconjugatedoctaphyrinringofOct-2Cucanbefullyrupturedduring electrolyticHex-2Cu-Ofeaturesabroadpeakthatcanbedecoupledto electrolysis. coordinatedCu2+(572.2eV)andsuperficiallyoxidizedCuδ+(569.8eV) The structural mutation of Hex-2Cu-O was also witnessed by species,whereaspost-electrolyticOct-2CushowsmajorlythesuperUV–vis spectroscopy.</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>After 10h of electrolysis at −1.2V, postficialCuδ+apartfromasmallshoulderofCu0(SupplementaryFig.20). electrolytic Hex-2Cu-O was dissolved in deoxygenated ethanol and ThiscorroboratestheviewthatOct-2Cucanbefullyreducedduring subjectedtoUV–vischaracterization.Comparedtothespectrumof electrolysis.Instarkcontrast,boththeXPSN1sandCu2pspectraof pristine Hex-2Cu-O, thatof the post-electrolytic Hex-2Cu-O exhibits Hex-2Cu-2O before and after electrolysis remain mostly unchanged twonewabsorptionsat602and741nm,whicharealsoobservedon (SupplementaryFigs.21and22).Consequently,ourXPSanalyseson thechemicallyreducedHex-2Cu-ObyreactingwithNaBH (Supplethe three compound catalysts before and after electrolysis further 4 mentaryFig.13).Ingeneral,theUV–visspectrumofpost-electrolytic attesttothegoodelectrochemicalstabilityofHex-2Cu-2O,theeasily Hex-2Cu-Ocontainssignaturesfromboththepristineandchemically fragmentedOct-2Cu,andthepartiallyreducedHex-2Cu-O. reduced Hex-2Cu-O, confirming that Cu centers in Hex-2Cu-O are TovisualizetheHex-2Cu-OcomplexloadedontoKBbeforeand partially stripped.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4426,27 +7468,55 @@
           <t>S0261</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>This step isthe potential-determine step (PDS) with a 2+ especially the alcohols.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4468,27 +7538,55 @@
           <t>S0262</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Thus, the fundamental selectivity issues of pathways for CORtowardsmethane (C 1 )and C 2(+) productson CO R on Cu is a challenge of great importance in catalysis and Cu(100).</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>The COH/C-H (grey) pathway leads to C as the only 2 1 sustainableenergytechnologies.Substantialfocushasbeenmadein productwhereastheOCCOH(magenta)andCOH/OC-C(black) enhancingtheselectivityofC productsforCO R5–11. pathways both result in significant C production through a 2 2 2 A number of strategies have been developed to address the common intermediate dicarbon oxide (CCO*).</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>A degree of rate challengeofregulatingC Oxy/HCselectivityforCO RonCu-based control analysis shows that the total COR rate depends on 2 2 catalysts, including facet engineering12,13, nanostructuring14,15, energies of key surface species essentially present in the reaction oxide-derivedCu(OD-Cu)6,11,16,alloying9,17,18,andrunningCO R pathwayswithaPETnumber(n,relativetoCO)oflessthantwo 2 intandem7.Specifically,directreductionofcarbonmonoxide(COR) (SupplementaryFig.3)35.Inotherwords,reactionstepslaterinn atalkalineconditionshasbeenwidelyreportedtoyieldsignificantC than CCO* only play a role in controlling the selectivity of C 2 2 Oxyspecies at more positive potentials thanCOR19.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4510,19 +7608,47 @@
           <t>S0263</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>The predicted rate of ethylene relative to ethanol/ intermed 2 iates thro 2 ugh reduction of OCHCH* are demonstrated acetateonCu(100)isevenhigherthanthatexperimentally obtainedonpcCu,whichisinagreementwithobservations to be less favorable (Supplementary Fig. 8).</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>The above analysis by Hori et al.12. suggeststhatthepossibleC productsfromtheOCHCHpathway 2 ● In the low-current-density kinetically-controlled region are limited to acetaldehyde and ethanol (Fig. 2d). and at pH13, the potential dependencies of ethylene, The CH CO pathway.</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Adsorbed CH CO* tends to detach from ethanol, and acetate are slightly different, indicated by a 2 2 steeper Tafel slope for ethylene than for ethanol and the surface and generate molecular ethenone in solution.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4544,19 +7670,47 @@
           <t>S0264</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ethylene and ethanol are of great interest because they are economically and energetically valuable and are produced in substantial quantities globally (&gt; 30 MtC/yr)2.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Literature has found that these two products share the same generation pathway after C-C coupling5,6, which is believed to be the rate-determining step (RDS) of C product formation7–9.</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Considering that C-C 2+ coupling usually requires a high surface CO coverage (i.e. high θ ), and that Cu is sluggish in *CO converting CO to *CO, tandem catalysts combining Cu and a CO-selective metal (Ag, Au, and 2 Zn) have shown to be advantageous in C product generation5,10–22. 2+ Taking advantage of the high electrical conductivity, eCO2RR activity, and cost-effectiveness, Cu-Ag bimetallic/alloy catalysts have been widely investigated18–20,23–29.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4578,27 +7732,55 @@
           <t>S0265</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>These Raman signals gradually disMott–Schottkycatalystplaysanessentialroleintheselectiveproduction appearwithin the potentialrange from −0.2 to −0.7V vs RHE, indiofC .Weemphasizeseveralelementsofthelow-coordinated 2+alcohols catingthecompletereductionofCu OtometallicCu.Incontrast,the Cu/CuOcatalystfortheupgradedCERperformance.Firstly,thefast 2 L 2 Cl–Cu O samples retain the characteristic Raman modes (2Γ− and electronexchangeandenhancedintermediateadsorptionatsynergistic 2 12 Γ− +Γ+ )evenatpotentialsgreaterthan−0.7V,suggestingthatthe rectifyinginterfaceregionsareduetothelowcoordinationandasym12 25 low-coordinatedCu /Cu OcanprotectCu+speciesagainstreduction metricelectronaggregationinsidetheCu/CuOcatalyst.Inaddition,the L 2 L 2 duetoacombinationofenvironmentalandstructuralfactors.Overall, excellent conductivity and charge difference of Cu+/Cu0 boost the Cu /Cu Ocatalystexhibitsastrongeradsorptioncapacityfor*COdue nucleophilicorelectrophilicadditionreactionprocessforC–CorC–C L 2 2 totherestrictedrotationandstretchingvibrationpeaksofadsorbed coupling.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Secondly, the fast electron transfer from Cu to Cu+ at the *COandtheCu–CObondataround274and358cm−1,respectively58. enhancedrectifyinginterfacecaninducelatticeshrinkage,inhibitingthe Specifically,thecoverageof*COiscloselycorrelatedwiththeintensity lossofresidualoxygenatomsresponsibleforstabilizingthechemical ratioofν(Cu−CO)toν(*CO)59.Importantly,theintensityratioofν(Cu valenceofCu+whenworkingwithresidualClatoms.ThecleanCu/CuO 2 −CO)toν(*CO)ofCu /Cu OishigherinthecaseofCu /Cu Ocomregionsensuresmoothabsorptionanddesorption,aswellasthecouL 2 L 2 paredtoCu /Cu O,implyingagreaterCOcoverage,whichisfavorable plingbehavioroftheoxyhydrocarbonintermediates.Thirdly,abundant P 2 fortheoxidationstateofCu+.Thepeaksobservedat1015,1024,and defectsoriginatedfromoxygenvacanciesandresidualCl,asaresultof 1069cm−1canbeassignedtothevibrationsofν(C–O)ofHCO −,OCO electrochemically reconstructing Cl–CuO, supply rich free electrons 1 3 2 antisymmetric stretching from *COOH, and ν (C–O) of CO 2−, andlandingsitesforadsorbedintermediates.Theseresultsworktoge2 3 respectively60.</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Furthermore, as the potential increases, CO 2− accutheronlow-coordinatedCu/CuOMott–Schottkycatalysttoimprove 3 L 2 mulates and disappears on the catalyst surface, indicating the theselectivityofC .Thefaradicefficiencyandenergyefficiency 2+alcohols NatureCommunications|( 2024)1 5:5172 7</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>P1:COCO</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4620,27 +7802,55 @@
           <t>S0266</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CO 2 reductionreaction(CO2RR)towardmulticarbonproductsby heterogeneouscopper-basedcatalysts.ACSCatal.10,1754–1768(2020). 12.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Wang,X.etal.Mechanisticreactionpathwaysofenhancedethyleneyields Operandodifferentialelectrochemicalmassspectrometry(DEMS).Operando duringelectroreductionofCO–COco-feedsonCuandCu-tandem Differentialelectrochemicalmassspectrometry(DEMS)wasdoneusingacustomelectrocatalysts.Nat.Nanotech 2 nol.14,1063–1070(2019). madeTUBerlinelectrochemicalcapillaryDEMSflowcell.DEMScapillaryflowcellis characterizedbyhavingawell-definedelectrolyteprofileflowovertheworking 13. f W ac a e n ti g n , g Y a . n e d ta p l r . o C m a o ta te ly s s r t e s n y e n w th a e b s le is f u u n el d s e e r le C c O tro 2 s e y l n ec th tr e o s r is e . d N uc a t t i . o C n a f t a a v l o . u 3 r , s 98–106 electrode.Thereactionproductsaretransportedintotheinterfaceliquidvacuum (2020). throughouta0.15mmglasscapillary.Thecollectionofhighconcentratedaliquotnear 14.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Burdyny,T.&amp;Smith,W.CO reductionongas-diffusionelectrodesandwhy catalystsurfaceandenhancedliquid-vacuuminterfaceallowsafastandathigh2 catalyticperformancemustbeassessedatcommercially-relevantconditions. i fl n o t w en c s e it l y lr d e e su te l c ts ti i o n n th o e fg d a is s t e r o ib u u s te p d ro fl d o u w ct o s. v T er h t e he hi h g y h d p ro e p rf h o o rm bic an m ce em w b it r h an D e E c M om S p c a a r p tm ill e a n ry t EnergyEnviron.Sci.12,1442–1453(2019). alsoknownasthecyclonicflow.Theinterfaceliquid/vacuumpromotedbyPTFE 15.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>P1:COCO</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4662,19 +7872,47 @@
           <t>S0267</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>11</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Hoang,T.etal.Nanoporouscopper–silveralloysbyadditive-controlled spectroscopy.J.Am.Chem.Soc.141,18704–18714(2019). electrodepositionfortheselectiveelectroreductionofCO toethyleneand 2 36.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Jiang,S.,Klingan,K.,Pasquini,C.&amp;Dau,H.NewaspectsofoperandoRaman ethanol.J.Am.Chem.Soc.140,5791–5797(2018). spectroscopyappliedtoelectrochemicalCO reductiononCufoams.J.Chem. 65.</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Dinh,C.etal.CO electroreductiontoethyleneviahydroxide-mediated 2 2 Phys.150,041718(2019). coppercatalysisatanabruptinterface.Science360,783–787(2018). 37.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4696,27 +7934,55 @@
           <t>S0268</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" t="n">
+        <v>8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>It corresponded Fig. 28, and Supplementary Data 1–1352.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>The *OCHO mechanwiththecompetingreactionofH andCH increasingwhenthe 2 4 ism was preferred for our catalysts than the *CO mechanisms, potential decreased.</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>* due to the production of CO was suppressed along with the CH 3 was the key intermediate for C 2+formation rates and it formation ofethanol atthepotentials below−0.8Vas shownin occurred when the potential decreased to −0.6V vs.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4738,19 +8004,47 @@
           <t>S0269</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" t="n">
+        <v>9</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>T in h c e lud ca ed tal a y n st e s th d a e n li o v l e F re E d of h 5 ig 1 h % C at 2+ the pr p o o d te u n ct t s ial F o E f− (~ 1 7 .1 3% V ) v , s w .R h H ic E h A ele ft c e t r r w oc a h rd em sw ic e al p s o ta u t r i e o d n K w H ith CO th 3 e s c o o lu p t p io er n t i a n p t e o . t T h h e e c o e r ll ga w n h ic ich gla w ss as u c p o p n e n r e c c o t v e e d r t o o f t t h h e e and the current density of −14.4mA/cm −2 in 0.1M KHCO cellwiththeAg/AgClreferenceelectrodewasusedtofixthedistancebetween 3 referenceelectrodeandworkingelectrodefromstarttofinish57.OperandoXAFS electrolyte.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Operando XAS and XPS results revealed a potentialdataweremeasuredwithfluorescencemodeusingtheAr-filledLytledetector. dependent structure transformation from CuO cluster to Cu –CuN moiety,whichisareversibleprocess.OnceCu –CuN n 3 2 3 clusters have been formed at −1.1V, CO conversion to ethanol OperandoSR-FTIRMeasurements.OperandoSR-FTIRmeasurementswere 2 occurswiththemaximumFE,indicatingtheCu -CuN clusteris conductedattheinfraredspectroscopyandmicrospectroscopystation(BL01B)of 2 3 NationalSynchrotronRadiationLaboratory(NSRL)58.TheCHI660Eelectrothe optimal site.</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The N-doping played an important role to dischemicalworkstation(ShanghaiChenhua,China)wasusedtoapplyvoltagetoa perse the reduced Cu n cluster uniformly and adjust charge disself-madeinfraredreflectioncell.Theinfraredspectrumswerecollectedusing tributionbetweenmetalatomsandsubstrate.OperandoFTIRand BrukerVertex70V/sFTIRspectrometerwithnitrogencooledmercurycadmium theoretic calculations results demonstrated that CH * was the telluridedetector,andthesynchrotronradiationinfraredbeamwasfocusedonthe major intermediates and Cu –CuN clusters wer 3 e chargereflectioncellusingBrukerHyperion3000microscopeequippedwitha×15 2 3 objective.Inthemeasurements,thegapbetweentheworkingelectrodeandthe asymmetric sites that are intensified by CH 3 * adsorbing.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4772,19 +8066,47 @@
           <t>S0270</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>This finding confirms the positive impact of Ag length of both dCu O/Au and dCu O/Ag catalysts are 2 2.3% 2 2.3% modification on CO RR.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>The degree of introduced Ag-dependent similar.Therefore,otherpotentialmechanismsondCu O/Ag 2 2 2.3% FEs ofproducts from these catalysts wasassessedunder the same need to be assessed for boosted CO RR performance. 2 currentdensity.AsisshowninFig.4b,c,increasingAgindCu O/ ReactionpathwaysforC H andEtOHproductionaresimilar 2 2 4 Ag leads to a volcano-shape for FE that corresponds with a on Cu surfaces, as they initiate with two adsorbed–CO EtOH reverse-volcano on FE , and contrasts with the monotonously dimerization followed by several steps of protonation and CO decreased FE for C H .</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
+          <t>This correlation between the amount of dehydration to generate a shared intermediate, * HCCOH3,14. 2 4 modified Ag and FEs for CO and EtOH was observed also with The selectivity between C H and EtOH, is significantly 2 4 other applied currents (Supplementary Fig. 22).</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4806,27 +8128,55 @@
           <t>S0271</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="n">
+        <v>7</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>This asymmetric C−C coupling has a lower energy 2 Ag result in tailored * CO configuration.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Given the different barrier than that for *CO dimerization as evidenced by the 2.3% electron * back-donating and proton-combining ability of reported theory studies19, which contributes to increased C 2+ adsorbed CO on atop and bridge Cu sites, the energy barrier production. for following * CO protonation is altered.</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Previous studies Additional peaks from ATR–IRAS spectra at ~1567 and demonstrate that * CO bridge protonation is more energetically ~1182cm −1 and ~1336 and ~1117cm −1 were analyzed.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4848,19 +8198,47 @@
           <t>S0272</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Therefore we hypothesize that triggered * CO and * CO adsorption that triggers asymmetric C–C asymmetric C−C coupling on dCu 2 O/Ag 2.3% boosts C 2+ coup b l r i i n d g ge after * CO b a r t i o d p ge protonation.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Because of the relatively low production and favors EtOH pathway via stabilizing pivotal oxygen affinity and unsaturated nature of the C H intermediates 2 4 intermediates. compared with EtOH, the asymmetric C–C coupling provides an Inaddition,thepeakfortheabsorbedbicarbonateat1547cm −1 unbalanced coordination environment that is beneficial for EtOH on dCu 2 O/Ag 2.3% is missing compared with dCu 2 O and dCu 2 O/ intermediateformationandstabilizationinlowerenergythanthat Au 2.3% ,confirmingthatthevalueofthelocalpHontheelectrode for C 2 H 4 ,and thereby promotes the pathway for EtOH. ofdCu O/Ag isgreaterthanthatfordCu OanddCu O/Au 2 2.3% 2 2 2.3% during CO RR47.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
+          <t>The high pH at the surface of electrode is 2 thought to favor C–C coupling by lowering the energy barrier of Discussion CO 2 activation and suppressing H 2 evolution, and contributes to In summary, an assessment of a newly synthesized, silvert C h O e 2 – b T oo P s D ted for ac d t C iv u it 2 y O/ f A or g 2.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4882,19 +8260,47 @@
           <t>S0273</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Because of the relatively low production and favors EtOH pathway via stabilizing pivotal oxygen affinity and unsaturated nature of the C H intermediates 2 4 intermediates. compared with EtOH, the asymmetric C–C coupling provides an Inaddition,thepeakfortheabsorbedbicarbonateat1547cm −1 unbalanced coordination environment that is beneficial for EtOH on dCu 2 O/Ag 2.3% is missing compared with dCu 2 O and dCu 2 O/ intermediateformationandstabilizationinlowerenergythanthat Au 2.3% ,confirmingthatthevalueofthelocalpHontheelectrode for C 2 H 4 ,and thereby promotes the pathway for EtOH. ofdCu O/Ag isgreaterthanthatfordCu OanddCu O/Au 2 2.3% 2 2 2.3% during CO RR47.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>The high pH at the surface of electrode is 2 thought to favor C–C coupling by lowering the energy barrier of Discussion CO 2 activation and suppressing H 2 evolution, and contributes to In summary, an assessment of a newly synthesized, silvert C h O e 2 – b T oo P s D ted for ac d t C iv u it 2 y O/ f A or g 2.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
+          <t>C 3% O a 2 R ls R o . ex M hi o b r i e t o a ve h r i , gh t e h r e te C m O p – e T ra P t D ure a f n o d r E m t o O d H ifie p d at c h o w p a p y er i - s o a x c id ce e le c r a a t t a e l d yst vi h a a t s ri c g o g n e fi ri r n m g e t d he th a a s t y t m he m C et O ri 2 c R C R – t C o CO 2 andCOdesorptionthanthosefordCu 2 OanddCu 2 O/Au 2.3 , coupling.AnoptimizeddCu 2 O/Ag 2.3% exhibitsaFEof40.8%and i a n n d d ica C ti O ng fo d r Cu e 2 ffi O c / i A en g t 2.3 C % O h 2 a R s R st a ro t n l g a e r r ge bo c n u d rr in en g t st ( r S e u n p g p th lem o e f n C ta O ry 2 b E o E o H s F te o d f E 2 t 2 O .3 H % p f a o r r tia E l tO cu H rre p n r t o d d e u n c s ti i o ty n o i f n 32 fl 6 o . w 4m ce A ll, cm to − ge 2 th at er − w 0. i 8 th 9 Fig. 30).</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4916,27 +8322,51 @@
           <t>S0274</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-31427-9 Fig.5InsituATR–IRASmeasurementandmechanismfordCu O/Ag .InsituATR–IRASobtainedduringchronopotentiometryinapotentialwindow 2 2.3% 0.2to−1.2V foradCu O,andbdCu O/Ag underCO RR.(Areferencespectrumobtainedat0.3V in1MKOHissubtracted).Potential RHE 2 2 2.3% 2 RHE dependenceofratioofc*CO /*CO andd*OC H /*OCCOHobtainedfordCu O,dCu O/Ag anddCu O/Au .eSchematicforboostedEtOH bridge atop 2 5 2 2 2.3% 2 2.3% generationoverdCu O/Ag .Yellow-color,gray,white,orange,red,andazurespheresinthemodelrepresentH,C,O,Cu1+,Cu0,andAgatoms, 2 2.3% respectively. dCu O/Ag (Fig.5d)42,43.Thisisattributedtotheasymmetric proposed (Fig. 5e).</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>At first, the coordinated pure-Cu surface is 2 2.3% C−C coupling induced unbalanced coordination environment, replaced with neighboring Ag atoms with modification by Ag in whichdisruptsthecoordinationsitesforC H intermediates,and Cu O and reduces these to CuAg alloy under CO RR.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4958,19 +8388,43 @@
           <t>S0275</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="n">
+        <v>14</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Figure 4 C-C bond formation via a formyl-bicarbonate coupling pathway (with a key intermediate 4).</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Reaction energy proles and the corresponding intermediate structures (0 to 7) for the formation of ethanol via the CO RR on the Sn -O3G catalyst.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4992,19 +8446,43 @@
           <t>S0276</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>This catalyst was found to maintain 97% of its initial activity after 100 hours of continuous reaction at a geometric current density as high as 17.8 mA·cm− 2.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>The C-C bond formation mechanism on this newly-developed tandem catalyst was elucidated by combining isotope (13CO and H13COOH) 2 labelling experiments with extensive density functional theory (DFT) studies, providing a highly ecient Page 3/14</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="N127" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5026,19 +8504,47 @@
           <t>S0277</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>This process can potentially generate a wide variety of products 4,5,6,7,8, among which the liquid compounds are preferred 9 because of their high energy densities (e.g., -1366.8 kJ/mol for CH CH OH) and ease of 3 2 storage when serving as substitutes for gasoline 10,11.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>However, due to the high energy barrier to C-C bond formation, which competes with the formation of C-H or C-O bonds 12,13,14, the generation of multi-carbon liquid products via the CO RR is still very dicult.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
+          <t>To date, Cu is the only electrocatalyst found able to 2 generate C (n ≥ 2) liquid products from the CO RR with appreciable reaction rates, due to the strong n 2 adsorption of the *CO intermediate on the Cu surface that promotes C-C bond formation via CO dimerization or CO-CHO coupling 5,12,15.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="N128" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5060,19 +8566,47 @@
           <t>S0278</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>7</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Two possible CO binding mechanisms were 2 assessed: monodentate (2 − 1) and side-on (2) 26,27 (Extended data Fig. 56a).</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Thus, there are two possible pathways for CO reduction, one of which produces CO and the other produces ethanol.</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Free energy 2 pathways for competing C1 and C2 products were systematically calculated as shown in Extended data Figs. 56–57 and Extended data Table 18.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5094,27 +8628,55 @@
           <t>S0279</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2.5 2.0 1.5 1.0 0.5 0.0 CA: 131° CA: 156° thechangesof*COand*Hcoverage.Ingeneral,awider*COadsorption whereθisthecoverageoffreesurfacesites,E istheCO adsorption COx x voltageindicatesahigher*COcoverageinin-situATR-SEIRASspectra, energyonthesurface,RistheidealgasconstantandTisthetemwhile a larger decay distance of fluorescence intensity via CLSM perature.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>The coverage of intermediate (θ ) is a function of CO COx representsalower*Hcoverage.Theexperimentaldatarevealthatthe adsorptionenergy(E )andlocalCO concentration([CO]).Tovary COx x x increaseofhydrophobicitywillleadtoanincreasing*COcoverageand theintermediate(*CO/*H)coverage,changingthelocalconcentration adecreasing*Hcoverage(Fig.5b). ofreactant(CO)atthecatalystlayerratherthan*CO/*Hadsorption x Further,thereactionpathwaysoncatalystsurfaceswithdifferent energyis,therefore,apromisingapproach.Comparedwiththeclaswettability can be understood (Fig. 5c).</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>At equilibrium, the surface sicalmodulationoftheactivesite,thenoveltyofourmethodisthatthe coverageoftheintermediate(*CO,*H)isdirectlyproportionaltothe CO RRiscompletelycontrolledbykinetics(masstransport)through 2 concentration of reactants (CO , H O).</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5136,19 +8698,47 @@
           <t>S0280</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Interfacial hydrophobic treatment may accelerate CO mass nion Co., Ltd.) were used as the counter electrode (CE) and the 2 transport while hindering H O absorption, resulting higher *CO/*H reference electrode (RE), respectively.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>The cathode and anode 2 ratio.Thereactionlimitationmayshiftfrom*COinsufficiencyto*H compartment was separated by an anion exchange membrane exhausting, resulting in the main product changes from ethanol to (AEM,FAA-3-PK-75,Fumatech),bothofwhichwerefilledwith1M ethylene.ControllablewettabilitymodulationprotocolherecanelaKOHelectrolyte.CO (99.995%,AirLiquideCo.Ltd.)flowedintothe 2 borately balance the CO and H O mass transport, which specially cellataflowrateof20sccm(standardcubiccentimeterperminute) 2 2 synthesizes C product with highly selective in electrode design. controllingbyamassflowcontroller(MC-Series,AlicatScientific). 2+ Moreover,futureresearchendeavorsmayfocusonpromotingmodTo ensure the accuracy of the product selectivity calculation, erateandstablehydrophobicityonporouselectrodestofurtherboost anotherflowmeter(MC-Series,AlicatScientific)wasusedtoaccuactivityandselectivity. ratelymeasuretheoutletCO flowrate.Peristalticpumps(EC2002 01,GaossunionCo.,Ltd.)wereusedtocontroltheflowrateofthe Methods electrolytesat~10mLmin−1.Thegasproductswerequantifiedby PreparationofCuelectrode gas chromatography (GC) (Ruimin GC 2060, Shanghai), which is Cucatalyst(Cutarget,99.999%,ZhongnuoAdvancedMaterialTechonlineconnectedwiththeflowcell.COandH weredetectedbya 2 nologyCo.,Ltd.)wasdepositedontocarbonpapergasdiffusionlayers flameionizationdetector(FID)andthermalconductivitydetector (2×2cm2,Sigracet29BC,SGLCarbon)throughadirectcurrent(DC) (TCD),respectively.Theliquidproductswerequantifiedbyusing magnetronsputteringsystem.Thebasepressurewas2.0×10−4Pa,and static headspace gas chromatography (HS-GC, Agilent TechnolotheflowrateofArwassetas20standardcubiccentimetersperminute gies,7890B).AllpotentialswerenotiRcorrected.DuringtheCORR (sccm).TheDCpowerwas40W,andtheworkingpressurewas1Pa. experiment,acontinuouslyflowingCO/N mixedgas(CO:10sccm; 2 Thedepositiontimewas10min.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>N :20sccm)wasdirectedintothegascompartment. 2 NatureCommunications|( 2023)1 4:3575 8</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5170,19 +8760,47 @@
           <t>S0281</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Monkhorst–Pack 298K.Thekineticconstantforallelementarysteps(Supplementary k-pointsof2×2×1,3×2×1,and2×2×1wereusedforthe(111),(211), Table5)wasobtainedbasedontheArrheniusequation,asfollows: and (100) surfaces, respectively.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>The transition states were located usingthemethodofconstrainedoptimisationwhichhasbeenwidely (cid:3) E a ð13Þ used in many previous works18,24,25, with a force convergency of k=A×e RT, 0.05eVÅ−1 forboth structural optimizationand transition state calculations.Noprotonationbarrierswereconsideredinthemicrokinetic whereAreferstothepre-factor,Eareferstotheactivationbarrier,R modelling. referstothemolargasconstant,andTreferstothetemperature.The steady state was located at dθ/dt=0, and the reaction rate was Freeenergycorrections obtained,describedbytheproductionrateofC H . 2 4 Allcalculatedenergies,includingadsorptionandgasenergies,were correctedtothefreeenergyat298K,asfollows: COMSOLsimulations WeusedacommercialsoftwareCOMSOLtoperformthesimulation:43 E =EZPE+EU +EP +ES , ð9Þ ThepotentialandflowfieldsweregovernedbythePoissonequation, cor cor cor cor cor Stokesequations,andthecontinuityequationsasfollows: whereEZ co P r E isthezero-pointenergycorrection,EU cor andEP cor arethe X temperature (inner energy) and pressure corrections, respectively, ε∇2ψ= Fz i c i , ð14Þ and ES cor is the entropy correction (Supplementary Table 7).</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
+          <t>At i equilibrium,thechemicalpotentialofapairof(H++e−)ionsat0V RHE c is on r s e i f d e e r r r i e n d g to th a e s t c h o e m h p a u l t f at c io h n e a m l ica h l yd p r o o te g n e t n ial e o l f ect H r 2 od m e ole ( c C u H le E s ) ρ ∂ ∂ u t = (cid:3)∇p+μ∇2u(cid:3) X Fz i c i ∇ψ, ð15Þ approximation42.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="N132" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5204,19 +8822,47 @@
           <t>S0282</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>This allows us to identify crucial Cu sites and surface intermediates for either ethylene or ethanol, Potential-dependent intermediate evolution leading to the definition of an updated reaction scheme for CORR to To reveal molecular insights into C–C coupling intermediates and 2 C products. their potential dependence, we carried out in situ SERS measurements 2 (Supplementary Fig. 7).</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Figure 2a shows the in situ Raman spectra Electrode preparation and CO RR test acquired at the same position on the electrochemically treated Cu 2 The Cu electrodes were prepared by an electrochemical oxidation– foil electrode as a function of the applied potential in a CO-saturated 2 reduction process (see Methods for details).</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Scanning electron micros0.1 M NaClO electrolyte.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5238,19 +8884,47 @@
           <t>S0283</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>6</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Furthermore, from −0.85 V RHE OD-Cu sites (Supplementary Fig. 24 and Supplementary Table 16). onwards, undercoordinated distorted sites with high surface strain Besides, both crystalline and distorted morphologies with coordinaand deep s-band states originate (Fig. 5c,e) and enable the formation tion number below 8 show strong CO binding (&lt;−0.2 eV). of OCHCH at the surface (Fig. 6b), detected experimentally through 2 Localized compressive strain plays a crucial role in stabilizing Raman spectroscopy (Figs. 2c and 3) together with the production of *OCHCH species on distorted sites (red empty data points in Fig. 6a). ethanol (Fig. 1f). 2 In fact, *OCHCH formation energies increase following the increA careful comparison of ethylene, ethanol and methane Fara2 ment of compressive strain, and stronger binding is observed on daic efficiency versus CO selectivity (taken from Fig. 1f) confirms the undercoordinated distorted sites rather than crystalline sites.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Such existence of key differences between the ethylene and ethanol routes difference between crystalline and distorted sites can be ascribed (Fig. 6c).</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Instead, the similar dependence of ethanol and methane to their s-band states (Supplementary Table 16).</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5272,27 +8946,55 @@
           <t>S0284</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Instead, on crystalline domains such as Cu facand strain are heavily affected by the nature of active sites (Supets and adatoms, both parameters correlate (Supplementary Fig. 23), plementary Note 2). suggesting a mutual dependence of coordinationand strain-based Overall, these insights highlight a clear correlation between active linear scaling relationships for crystalline sites47,48. sites and product distribution.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Undercoordinated Cu sites enable To sample the reactivity of such surface defects, we estimated strong *CO binding, thus sustaining a high CO coverage on the surface, the binding energy of atop *CO and *OCHCH versus N and which opens the ethylene pathway via an OCCO(H) intermediate, 2 Cu–Cu Σ(Δd/d)N −1.</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>*CO was taken as a C selectivity descriptor10, whereas explaining the evidence of CH as the only C product observed at Cu–Cu 2+ 2 4 2+ *OCHCH binding strength was used as a descriptor of OCHCH stability −0.76 V (Fig. 1f).</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="N135" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5314,19 +9016,47 @@
           <t>S0285</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="n">
+        <v>9</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>After the electrochemical treatment, the samples were Σ(Δd/d)N−1 (j)= ∑ (6) Cu−Cu N−1 (j) rinsed with Ar-saturated HO and subsequently transferred under an i=1 Cu−Cu 2 Ar atmosphere into the load-lock of the UHV system.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>DFT details Visualization of vibrational fingerprints The DFT calculations were performed using the Vienna Ab initio To visualize vibrational frequencies of a given reaction intermediate Simulation Package34,35, with the Perdew-Burke-Ernzerhof (PBE) denin ioChem-BD37, it is necessary to follow the next steps, summarized sity functional33.</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
+          <t>We included dispersion according to the DFT-D2 in Supplementary Fig. 17. method53,54, with the re-parametrization of C coefficients for metals 6 performed by our group55.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="N136" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5348,27 +9078,55 @@
           <t>S0286</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="n">
+        <v>11</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Wang,X.etal.EfficientelectricallypoweredCO -to-ethanolvia spectroscopy.Energ.Environ.Sci.15,3968–3977(2022). 2 suppressionofdeoxygenation.Nat.Energy5,478–486(2020). 55.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Zhan,C.etal.RevealingtheCOCoverage-DrivenC-CCoupling 33.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Choi,C.etal.HighlyactiveandstablesteppedCusurfacefor MechanismforElectrochemicalCO ReductiononCu ONano2 2 enhancedelectrochemicalCO reductiontoCH .Nat.Catal.3, cubesviaOperandoRamanSpectroscopy.ACSCatal11, 2 2 4 804–812(2020). 7694–7701(2021). 34.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>P1:COCO</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="N137" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5390,19 +9148,47 @@
           <t>S0287</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="n">
+        <v>7</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Meanwhile, the overAgCuNW.Theincreased*COcoverageshallincreasetheprobatomicallydispersedAgatombecomespositivelycharged,matching ability of *CO-*CO coupling to form *COCO intermediate, directing wellwiththeXPSandXASresults.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>CO reduction to produce ethylene over AgCu NW (Supplementary 2 Operando Ramanmeasurements observed in-situ generation of Figs.61,62).</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
+          <t>*OHoverAgCuNWduringCO RR.Todeterminethe*OHadsorption Basedontheaboveresults,thereactionmechanismsofCO RRfor 1 2 2 site,theadsorptionanddissociationenergiesofH OonCuNW,AgCu thedistinctiveselectivitytowardsethyleneandethanoloverAgCuNW 2 NWandAgCuNWwerecalculated17.AsshowninFig.5a,comparedto andAgCuNWcanbeclearlyevidenced.Theethylenepathwayfollows 1 1 AgCuNWandCuNW,theH OadsorptionenergyoverAgCuNWis the symmetric C-C coupling, arising from the high *CO coverage 2 1 more negative with more electrons directly transferred from H O generatedoverAgnanoparticlesandthereducedenergybarrierfor 2 molecule to AgCu NW (Supplementary Fig. 50).</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="N138" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5424,19 +9210,47 @@
           <t>S0288</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="n">
+        <v>27</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Particularly, the electrons transfer from Cu to Co atop bridge induced by subsurface Co doping enhances the oxophilicity of surface metal sites, which in turn facilitates the formation and conversion of *CHCHO* intermediates in the form of surface-O bonds.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>This mechanism directs the subsequent protonation towards the EtOH pathway, and capturing the transition from *CHCO to *CHCHO*.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
+          <t>As expected, the optimal Co -Sub-CuS catalysts 0.050 exhibited a FE of nearly 80.0% with a partial current density of 602.0 mA cm-2 in a flow cell.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="N139" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5458,19 +9272,47 @@
           <t>S0289</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Therefore, steering the reaction towards EtOH A pathway after C-C coupling is crucial for achieving the desired directional selectivity for EtOH, alongside the ongoing focus on enhancing C-C coupling dynamics11,12,15.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Experimental observations suggest that *CO intermediates undergo C-C coupling process, followed by protonation of the α-C to generate the shared initial intermediate *CHCO7,9,15,16.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
+          <t>The subsequent protonation pathway of *CHCO, which forms a variable SDI in a tautomeric form, may play a decisive role in dictating the selectivity between C hydrocarbons (mainly C H ) and C 2 2 4 2 oxygenates (mainly EtOH), as revealed by density functional theory (DFT) calculations10,15-17.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="N140" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5492,19 +9334,47 @@
           <t>S0290</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" t="n">
+        <v>5</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>In current Cu-based 2 4 R catalysts system, however, the experimental identPification and induction of *CHCHO* from N *CHCO have not been reported, primarily due to the uncontrollable binding of O atoms and the I uncertainty surrounding the adsorption fo E rm of the SDI8-11,16,17.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Therefore, there is a pressing need L C to develop a rational and versatile catalyst design strategy to direct the branching SDI pathway I T toward EtOH, focusingR on controlling the adsorption configuration of oxygen-binding A intermediates (*CHCHO*).</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
+          <t>To date, strategies aimed at modifying surface oxophilicity have provided alternative routes to influence the adsorption configuration of oxygen-binding intermediates through techniques such as surface engineering20,21, doping effects22, alloying23,24, and interface engineering25.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="N141" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5526,19 +9396,47 @@
           <t>S0291</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" t="n">
+        <v>7</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>The K+-coordinated water (denoted as K+ H O) will con2 CA, the *OCCOH and *OC H were extraordinarily stronger in the tinuouslysupplyH Otoelectrodesurfaceaswellasacceleratedthe 2 5 2 intensities and dramatically easier than the formation of *CHO and HERkinetics,whichwasmoresignificantlyyeteffectivelyforHERthan *OCH intermediatesfortheformation ofCH ,distinctlyillustrating theothertwostructuraltypesofH O(2-,4-coordinatedH-bondwater, 3 4 2 that the C HOH and C products werefavorablyformed over the whichweredenotedas2-HBH Oand4-HBH O).Thein-situRaman 2 5 2+ 2 2 developed catalyst.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>In consequence, the CA dominated and had a spectraresultsexhibitedthattheproportionsofK+H OoverCucat2 determinedeffectonthechangeinCO RRselectivityonCucatalyst,in alystincreasedfrom6.6%to12.3%asthepotentialdecreasedfrom0to 2 whichthekey*COintermediatewasstabilized,resultinginafavored −1VintheelectrolytewithoutCA,aswellasanincreasefrom6.8%to C–C coupling kinetics and restricted directed *CO hydrogenation 10.7%intheelectrolytewithCAwaspresented(SupplementaryFig.18). process,ultimatelypromotedtheC productformationandinhibited ComparedwiththatoftheelectrolytewithoutCA,theproportionofK+ 2+ themethanation(Fig.5c).</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
+          <t>H OincreasedslowlyalongwithchangedpotentialonCuelectrodein 2 NatureCommunications|( 2025)1 6:8390 7</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="N142" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5560,19 +9458,47 @@
           <t>S0292</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Importantly, the Raman feature of improved to as early as −0.75 V in an oxygen-containing 2 2 RHE thesurfacehydroxylgroupisabsent,indicatingthatthepresence atmosphere(Fig.2a),whileintheabsenceofO ,itisnotobserved 2 of the surface hydroxyl group, rather than any oxidant such as untilamuchmorenegativepotentialof−0.95V (Fig.2d).We RHE H O , is central to the enhanced production rates.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>In addition, emphasize that an increase in the onset potential of at least 200 2 2 density functional theory (DFT) calculations show the beneficial mV for methane formation with oxygen indicates significantly roleofthesurfacehydroxylgroupinreducingtheenergybarriers acceleratedreactionkinetics,becauseanincreaseinoverpotential in the formation of oxygenates and hydrocarbons.</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
+          <t>Results on this scale could lead to a significant rise in reaction rates reported in this work demonstrate the promise of enhancing the (depending on the Tafel slope) assuming the reaction is CO RR performance by leveraging coupled reactions via cokinetically controlled near the onset potential.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="N143" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5594,27 +9520,55 @@
           <t>S0293</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" t="n">
+        <v>6</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>Notably, these decreases are dimerization decrease as the *OH coverage increases from 0 to much more significant than those in *CO dimerization, which 3/9butreboundwithfurtherincreasein*OHcoverage(Fig.5a). agreeswiththesignificantanodicshiftofmethaneonsetpotential Boththeinitialstateandtransitionstatebecomelessstableasthe in the presence of the concurrent ORR (Fig. 2).</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>The energies of *OH coverageincreases.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="N144" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5636,19 +9590,47 @@
           <t>S0294</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Various strategies have been developed to enhance 2 during CORR, accompanied by a reaction-driven redisperthe performance of Cu-based catalysts, including nanostruc2 sion of Ag on the CuO NCs.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Data from operando surfaceturing Cu (control of exposed facets, defects and lowx enhanced Raman spectroscopy further uncovered significant coordinatedsites),[5]engineeringtheCu–electrolyteinterface variations in the CO binding to Cu, which were assigned to (changeoflocalpH),[6]andadjusting theCu oxidationstate Ag@CusitesformedduringCORRthatappearcrucialforthe (compositional change).[7] For example, CuO nanocubes 2 2 C@Ccouplingandtheenhancedyieldofliquidproducts.</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(NCs) with well-ordered (100) facets have been shown to lead to an increase in the selectivity toward ethylene, while Introduction suppressingmethaneproduction.[5e,8] A promising way to further improve the catalystQs Inthequestfordevelopingasustainableenergyeconomy, performanceandselectivityistheintroductionofasecondary the electrochemical reduction of carbon dioxide (CORR) metal.[9]RecentstudiesofCu–Agbimetallicsystemsshowed 2 into value-added chemicals and fuels offers the potential to enhancedselectivityforC products.Inparticular,aphase2+ close the anthropogenic carbon cycle and store renewable blendedAg-CuOcatalysthadathreetimeshigherFaradaic 2 (wind,solar,hydro)energyintochemicalbonds.[1]Ithasbeen efficiency (FE) toward ethanol than Ag-free CuO, but 2 therefore of particular interest to develop efficient and sufferedfromlowactivity(jj j&lt;1mA).[10]Additionally, ethanol selective electrocatalysts, which reduce the reaction overAg-coveredCuOnanowirespreparedviaagalvanicreplace2 potential and steer the reaction toward hydrocarbons and ment reaction enabled a 1.4times higher current density multicarbon oxygenates (C ).</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5670,19 +9652,47 @@
           <t>S0295</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Data from operando surfaceturing Cu (control of exposed facets, defects and lowx enhanced Raman spectroscopy further uncovered significant coordinatedsites),[5]engineeringtheCu–electrolyteinterface variations in the CO binding to Cu, which were assigned to (changeoflocalpH),[6]andadjusting theCu oxidationstate Ag@CusitesformedduringCORRthatappearcrucialforthe (compositional change).[7] For example, CuO nanocubes 2 2 C@Ccouplingandtheenhancedyieldofliquidproducts.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>(NCs) with well-ordered (100) facets have been shown to lead to an increase in the selectivity toward ethylene, while Introduction suppressingmethaneproduction.[5e,8] A promising way to further improve the catalystQs Inthequestfordevelopingasustainableenergyeconomy, performanceandselectivityistheintroductionofasecondary the electrochemical reduction of carbon dioxide (CORR) metal.[9]RecentstudiesofCu–Agbimetallicsystemsshowed 2 into value-added chemicals and fuels offers the potential to enhancedselectivityforC products.Inparticular,aphase2+ close the anthropogenic carbon cycle and store renewable blendedAg-CuOcatalysthadathreetimeshigherFaradaic 2 (wind,solar,hydro)energyintochemicalbonds.[1]Ithasbeen efficiency (FE) toward ethanol than Ag-free CuO, but 2 therefore of particular interest to develop efficient and sufferedfromlowactivity(jj j&lt;1mA).[10]Additionally, ethanol selective electrocatalysts, which reduce the reaction overAg-coveredCuOnanowirespreparedviaagalvanicreplace2 potential and steer the reaction toward hydrocarbons and ment reaction enabled a 1.4times higher current density multicarbon oxygenates (C ).</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The selective generation of toward ethylene production as compared to pure CuO 2+ 2 liquidproductssuchasethanol,1-propanol,andacetaldehyde nanowires.[11] Furthermore, CuAg surface alloys have been is highly desirable due to their high energy densities and foundtobemoreselectivefortheformationofmulti-carbon advantages for storage/transport as compared to gaseous products than pure copper.[12] The facilitated yield of C 2+ products.[2] products in the bimetallic system is usually linked to the suppression of HER due to the enhanced coverage of *CO adsorbates as compared to *H,[12b] and the diffusion of CO [*] A.Herzog,Dr.A.Bergmann,Dr.H.S.Jeon,Dr.J.Timoshenko, from Ag sites to Cu sites that enables C@C coupling (CO Dr.S.Kfhl,C.Rettenmaier,M.LopezLuna,F.T.Haase, spillover).[10,11] Note here that a short diffusion path of CO Prof.Dr.B.RoldanCuenya DepartmentofInterfaceScience and therefore a homogeneous distribution of Cu and Ag at Fritz-HaberInstituteoftheMax-PlanckSociety the surface of the catalyst are essential for an effective CO Faradayweg4–6,14195Berlin(Germany) spillover.[10,12b]Nonetheless,althoughthespatialarrangement E-mail:roldan@fhi-berlin.mpg.de ofCuandAginthesestudiesseemstoplayakeyroleforthe SupportinginformationandtheORCIDidentificationnumber(s)for differentCORRselectivitytrendsobtained,thekeyparamtheauthor(s)ofthisarticlecanbefoundunder: 2 eters for achieving an optimal synergy in Cu–Ag bimetallic https://doi.org/10.1002/anie.202017070. systems are still unknown.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5704,19 +9714,47 @@
           <t>S0296</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" t="n">
+        <v>6</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>No relationship is clearly observed, (Supplementary Fig. 28).</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Overall our ex situ and operando emphasizingthattheoriginoftheimprovedselectivityforC 2+is characterizations of the modified bimetallic catalyst establish an not primarily due to the surface properties of the Cu electrodes obvious correlation between the electron-withdrawing ability of but rather the electron-withdrawing nature of the aromatic the functional groups and the oxidation state of Cu, which heterocycles as evidenced by our operando X-ray absorption translate into a larger concentration of adsorbed *CO on the spectroscopy measurements (Supplementary Figs. 6, 24 and 25). electrode surface and ultimately a higher probability for *CO to Itiswell-knownthattheformationofmulticarbonproductsin dimerize.</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
+          <t>CO RRproceedsviatheformationofthe*COintermediate,and 2 its subsequent dimerization in CO=CO or *CO–COH intermediates57–59.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="N147" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5738,27 +9776,55 @@
           <t>S0297</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" t="n">
+        <v>6</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>As predicted by by online gas chromatography (GC, Agilent 7890B), equipped with a thermal density functional theory modelling11,34,35 and corroborated also conductivity detector and a flame ionization detector.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Liquid products were analysed after each measurement with a high-performance liquid chromatograph by recent experimental infrared spectroscopy and in situ XAS (Shimadzu Prominence), equipped with a NUCLEOGEL SUGAR 810 column and data36, the asymmetry between CO adsorption energies on metala refractive index detector, and a liquid GC (Shimadzu 2010 plus), equipped with a lic and oxidized copper sites facilitates CO dimerization and is fused silica capillary column and a flame ionization detector.</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Each presented data essential for C product formation34.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="N148" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5780,19 +9846,47 @@
           <t>S0298</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" t="n">
+        <v>11</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>The total 50μLDMSOsolutionand100μLD Ointo400μLoftheelectrolyte energy and force thresholds for geometry optimizations were 2 solution.Allproductconcentrationswerequantifiedbyintegrating 1×10−5eVand0.05eV/Å,respectively.TheminimumenergypaththeGCandNMRpeakarea. way (MEP) was examined using six images during the transition statesearch.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Each transition state was confirmed to have a single OperandoATR-SEIRASmeasurements imaginaryvibrationalfrequencyalongthereactioncoordinate,as Generally, a layer of 100nm Au film was deposited onto the showninSupplementarySupplementaryTable10.DFT-calculated reflectingplaneofaSiprismbyvacuumevaporationusingathermal activationenergybarrierE (U )canbeextrapolatedtopotentialU a 0 evaporator(PuDivacuumPD-400).BeforetheAudeposition,theSi bythefollowingequation53: prismwaspolishedwith0.05μmAl 2 O 3 suspensionandcleanedby (cid:1) (cid:3) (cid:1) (cid:3) sonicationsequentiallyinthebathsofacetoneanddeionizedwater.</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
+          <t>E a ðUÞ=E a U 0 +eβ0 U(cid:1)U 0 ð3Þ The working electrode was made by airbrushing the catalyst ink onto theaboveprepared Au film.TheATR-SEIRAS measurements where U is the equilibrium potential for the relevant elementary 0 wasconductedinatwo-compartmentspectroelectrochemicalcell reductionreactionstep,andβ’isthereactionsymmetryfactor,which comprising three electrodes including the working electrode, a wasapproximatedtobe0.49forthemodelsinthiswork54.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="N149" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5814,19 +9908,47 @@
           <t>S0299</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Their chemical structures are Inthecontrolled-potentialelectrolysis(CPE)from–0.9to–1.5V confirmed by UV–Vis (Fig. 1d) and Mass spectroscopy (Supple- (vs RHE without iR correction, all potentials are referenced to this mentary Figs. 2–4), matching well with the literature results23,24 format hereafter unless specifically noted), Hex-2Cu-O produces and theoretical values.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>For Hex-2Cu-O, each of the two copper mainlyCOandformateatlowoverpotentials(Fig.2a).Startingfrom ions is bound to one bridging meso-oxygen atom and three pyr- −1.1V and beyond, C products including ethylene, ethanol and n2+ rolic nitrogen atoms in a distorted quadrilateral configuration. propanolconstitutethemainCO RRproducts.Inparticular,at−1.2V 2 The central Cu–O–Cu bonding fights against the tension of the thetotalFaradaicefficiency(FE)ofmulti-carbonalcoholsincreasesto expandedporphyrin,resultinginagabledstructurewithaCu–Cu 50.8%(ethanol:32.5%;n-propanol:18.3%),whichhasbeenrarelyseen distanceof3.7Å(Fig.1a).InHex-2Cu-2O,thedoublyN-confused intheliterature(SupplementaryTable2).At−1.3V,thetotalFEofC 2+ hexaphyrinprovidestwocarbonyloxygenstoallowbothcopper products reaches to its maximum of 71% (Supplementary Fig. 6). ions to be independently anchored by the surrounding three N Afterwards,boththeFEsofethanolandn-propanoldecreases,whereas and one O atoms, also in a square-planar geometry but with theFEandpartialcurrentdensityofethylene continuallyrise (Supmilder Cu-O strain.</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>As a result, the overall structure of the macplementaryFig.7).At−1.5V,theFEofethyleneincreasesto34%,surrocycleisplanarwithaCu–Cudistanceof4.9Å(Fig.1b).Oct-2Cu passingthealcoholswithatotalFEof27%.Theseobservationssupport has a C symmetry with the two copper atoms bound to two the common view that the yield of oxygenates, compared to their 2 NatureCommunications|( 2022)1 3:5122 2</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5848,19 +9970,47 @@
           <t>S0300</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" t="n">
+        <v>4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>No Cu2+ state was ginalmacrocycles(i.e.Oct-2CuorOctaphyrin)otherthanabunchof observed in the Cu 2p spectrum of Oct-2Cu after electrocatalysis fragmentsbelowm/z=1100(SupplementaryFig.12).Thisindicatesthe (SupplementaryFig.19).FurtherintheAugerCuLMMspectra,postconjugatedoctaphyrinringofOct-2Cucanbefullyrupturedduring electrolyticHex-2Cu-Ofeaturesabroadpeakthatcanbedecoupledto electrolysis. coordinatedCu2+(572.2eV)andsuperficiallyoxidizedCuδ+(569.8eV) The structural mutation of Hex-2Cu-O was also witnessed by species,whereaspost-electrolyticOct-2CushowsmajorlythesuperUV–vis spectroscopy.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>After 10h of electrolysis at −1.2V, postficialCuδ+apartfromasmallshoulderofCu0(SupplementaryFig.20). electrolytic Hex-2Cu-O was dissolved in deoxygenated ethanol and ThiscorroboratestheviewthatOct-2Cucanbefullyreducedduring subjectedtoUV–vischaracterization.Comparedtothespectrumof electrolysis.Instarkcontrast,boththeXPSN1sandCu2pspectraof pristine Hex-2Cu-O, thatof the post-electrolytic Hex-2Cu-O exhibits Hex-2Cu-2O before and after electrolysis remain mostly unchanged twonewabsorptionsat602and741nm,whicharealsoobservedon (SupplementaryFigs.21and22).Consequently,ourXPSanalyseson thechemicallyreducedHex-2Cu-ObyreactingwithNaBH (Supplethe three compound catalysts before and after electrolysis further 4 mentaryFig.13).Ingeneral,theUV–visspectrumofpost-electrolytic attesttothegoodelectrochemicalstabilityofHex-2Cu-2O,theeasily Hex-2Cu-Ocontainssignaturesfromboththepristineandchemically fragmentedOct-2Cu,andthepartiallyreducedHex-2Cu-O. reduced Hex-2Cu-O, confirming that Cu centers in Hex-2Cu-O are TovisualizetheHex-2Cu-OcomplexloadedontoKBbeforeand partially stripped.</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>For comparison, the UV–Vis spectrum of postafter electrolysis, high-angle annular dark-field and aberrationelectrolyticHex-2Cu-2Oremainsunchangedafterthesame10-heleccorrected scanning transmission electron microscopy (HAADFtrolysis at −1.2V (Supplementary Fig. 14), which echoes previous STEM)wasemployed.Figure3aconfirmsthebicentricconfigurationof observationfrommassspectrometry.TheUV–Visspectrumofpostpristine Hex-2Cu-O, revealing isolated diatomic Cu pairs dispersed electrolyticOct-2Cushowsonlyafewweakabsorptionsuponlosing ontothecarbonsupport.Thecorrespondingline-scanprofiledisplays mostoftheoriginaloctaphyrinsignatures,providingfurtherevidence abimodalspacingofca.3.7Å(Fig.3b),closelymatchingthetheoretical forthecleavageoftheOct-2Cumacrocycles(SupplementaryFig.15).</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>no</t>
         </is>
